--- a/doc/ready/Fin_Model_Microgreen_Uzbekistan.xlsx
+++ b/doc/ready/Fin_Model_Microgreen_Uzbekistan.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -521,7 +521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M1 — bugungi FAKT: 5 restoran + 15 oila = 20 mln so'm/oy (Ariza, 32-band). O'sish shu nuqtadan hisoblanadi.</t>
+          <t>M1 — bugungi FAKT: 12 restoran + 15 oila (obuna) + ~205 chakana xarid = 40,000,000 so'm/oy. O'sish shu nuqtadan.</t>
         </is>
       </c>
     </row>
@@ -664,85 +664,85 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="Z5" s="6" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oilalar (B2C)</t>
+          <t>Oilalar (obuna)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
@@ -752,318 +752,400 @@
         <v>16</v>
       </c>
       <c r="D6" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="F6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="F6" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="G6" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="I6" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="H6" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="J6" s="5" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="L6" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="R6" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="M6" s="5" t="n">
+      <c r="S6" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="T6" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="N6" s="5" t="n">
+      <c r="U6" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="V6" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="O6" s="5" t="n">
+      <c r="W6" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="X6" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="Y6" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="P6" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="R6" s="5" t="n">
-        <v>78</v>
-      </c>
-      <c r="S6" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>92</v>
-      </c>
-      <c r="U6" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="V6" s="5" t="n">
-        <v>108</v>
-      </c>
-      <c r="W6" s="5" t="n">
-        <v>116</v>
-      </c>
-      <c r="X6" s="5" t="n">
-        <v>124</v>
-      </c>
-      <c r="Y6" s="5" t="n">
-        <v>132</v>
-      </c>
       <c r="Z6" s="6" t="n">
-        <v>132</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>JAMI MIJOZLAR</t>
+          <t>DOIMIY MIJOZLAR</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I7" s="8" t="n">
         <v>44</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="L7" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="N7" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="O7" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="P7" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="N7" s="8" t="n">
-        <v>71</v>
-      </c>
-      <c r="O7" s="8" t="n">
-        <v>77</v>
-      </c>
-      <c r="P7" s="8" t="n">
-        <v>84</v>
-      </c>
       <c r="Q7" s="8" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="R7" s="8" t="n">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="W7" s="8" t="n">
-        <v>144</v>
+        <v>89</v>
       </c>
       <c r="X7" s="8" t="n">
-        <v>153</v>
+        <v>91</v>
       </c>
       <c r="Y7" s="8" t="n">
-        <v>162</v>
+        <v>95</v>
       </c>
       <c r="Z7" s="6" t="n">
-        <v>162</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yangi mijozlar</t>
+          <t>Chakana xaridlar (dona/oy)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1</v>
+        <v>210</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3</v>
+        <v>220</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3</v>
+        <v>230</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>4</v>
+        <v>245</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>4</v>
+        <v>260</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>4</v>
+        <v>275</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>5</v>
+        <v>290</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>5</v>
+        <v>305</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>5</v>
+        <v>320</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>5</v>
+        <v>335</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>6</v>
+        <v>350</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>6</v>
+        <v>365</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>6</v>
+        <v>380</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>7</v>
+        <v>395</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>8</v>
+        <v>410</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>7</v>
+        <v>425</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>8</v>
+        <v>440</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>9</v>
+        <v>455</v>
       </c>
       <c r="U8" s="5" t="n">
-        <v>9</v>
+        <v>470</v>
       </c>
       <c r="V8" s="5" t="n">
-        <v>9</v>
+        <v>485</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="X8" s="5" t="n">
-        <v>9</v>
+        <v>515</v>
       </c>
       <c r="Y8" s="5" t="n">
-        <v>9</v>
+        <v>530</v>
       </c>
       <c r="Z8" s="6" t="n">
-        <v>142</v>
+        <v>530</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Yangi mijozlar</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="W9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="X9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z9" s="6" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Churn (oylik, %)</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="J9" s="9" t="n">
+      <c r="J10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="K10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="M10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="N9" s="9" t="n">
+      <c r="N10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="O9" s="9" t="n">
+      <c r="O10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="P9" s="9" t="n">
+      <c r="P10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="Q10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="R10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="S9" s="9" t="n">
+      <c r="S10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="T9" s="9" t="n">
+      <c r="T10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="U9" s="9" t="n">
+      <c r="U10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="W10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="X9" s="9" t="n">
+      <c r="X10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="Y9" s="9" t="n">
+      <c r="Y10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="Z9" s="10" t="n">
+      <c r="Z10" s="10" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -1100,7 +1182,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Mahsulot/Xizmat</t>
+          <t>Kanal / Mahsulot</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1122,25 +1204,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Restoran obunasi (Standard, oylik)</t>
+          <t>Restoran — bitta yetkazish cheki</t>
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>2500000</v>
+        <v>200000</v>
       </c>
       <c r="C4" s="12" t="n">
-        <v>192.31</v>
+        <v>15.38</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Modelda B2B ARPU shu narxdan hisoblanadi</t>
+          <t>Oyiga ~5 marta yetkazamiz → 1,000,000 so'm/oy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oila obunasi (o'rtacha, oylik)</t>
+          <t>Oila obunasi (oylik)</t>
         </is>
       </c>
       <c r="B5" s="11" t="n">
@@ -1151,25 +1233,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Haftalik va premium paketlarning o'rtachasi</t>
+          <t>Yagona haqiqiy obuna kanali</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Chakana savdo — o'rtacha chek</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mijozlar donalab oladi, eng katta oqim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Premium qulupnay (1 kg)</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B7" s="11" t="n">
         <v>110000</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C7" s="12" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Qulupnay daromadi shu narxdan hisoblanadi</t>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Yangi ferma mahsuloti, asosan chakanaga</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1380,89 +1480,89 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B2B (restoranlar)</t>
+          <t>Restoranlar (buyurtma)</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>12500000</v>
+        <v>12000000</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>12500000</v>
+        <v>12000000</v>
       </c>
       <c r="D4" s="5" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>15000000</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>17500000</v>
-      </c>
-      <c r="F4" s="5" t="n">
+      <c r="G4" s="5" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>19000000</v>
+      </c>
+      <c r="K4" s="5" t="n">
         <v>20000000</v>
       </c>
-      <c r="G4" s="5" t="n">
-        <v>22500000</v>
-      </c>
-      <c r="H4" s="5" t="n">
+      <c r="L4" s="5" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="P4" s="5" t="n">
         <v>25000000</v>
       </c>
-      <c r="I4" s="5" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="J4" s="5" t="n">
+      <c r="Q4" s="5" t="n">
+        <v>26000000</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>27000000</v>
+      </c>
+      <c r="S4" s="5" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="U4" s="5" t="n">
         <v>30000000</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v>32500000</v>
-      </c>
-      <c r="L4" s="5" t="n">
+      <c r="V4" s="5" t="n">
+        <v>31000000</v>
+      </c>
+      <c r="W4" s="5" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="X4" s="5" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="Y4" s="5" t="n">
         <v>35000000</v>
       </c>
-      <c r="M4" s="5" t="n">
-        <v>37500000</v>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v>42500000</v>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="R4" s="5" t="n">
-        <v>52500000</v>
-      </c>
-      <c r="S4" s="5" t="n">
-        <v>55000000</v>
-      </c>
-      <c r="T4" s="5" t="n">
-        <v>60000000</v>
-      </c>
-      <c r="U4" s="5" t="n">
-        <v>62500000</v>
-      </c>
-      <c r="V4" s="5" t="n">
-        <v>65000000</v>
-      </c>
-      <c r="W4" s="5" t="n">
-        <v>70000000</v>
-      </c>
-      <c r="X4" s="5" t="n">
-        <v>72500000</v>
-      </c>
-      <c r="Y4" s="5" t="n">
-        <v>75000000</v>
-      </c>
       <c r="Z4" s="6" t="n">
-        <v>977500000</v>
+        <v>542000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B2C (oilalar)</t>
+          <t>Oila obunalari</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
@@ -1472,565 +1572,647 @@
         <v>8000000</v>
       </c>
       <c r="D5" s="5" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="E5" s="5" t="n">
         <v>9000000</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="F5" s="5" t="n">
         <v>10000000</v>
       </c>
-      <c r="F5" s="5" t="n">
-        <v>11500000</v>
-      </c>
       <c r="G5" s="5" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="I5" s="5" t="n">
         <v>13000000</v>
       </c>
-      <c r="H5" s="5" t="n">
-        <v>14500000</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>16500000</v>
-      </c>
       <c r="J5" s="5" t="n">
-        <v>18500000</v>
+        <v>14000000</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>20500000</v>
+        <v>15000000</v>
       </c>
       <c r="L5" s="5" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>19000000</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="R5" s="5" t="n">
         <v>22500000</v>
       </c>
-      <c r="M5" s="5" t="n">
+      <c r="S5" s="5" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="T5" s="5" t="n">
         <v>25000000</v>
       </c>
-      <c r="N5" s="5" t="n">
+      <c r="U5" s="5" t="n">
+        <v>26000000</v>
+      </c>
+      <c r="V5" s="5" t="n">
         <v>27500000</v>
       </c>
-      <c r="O5" s="5" t="n">
+      <c r="W5" s="5" t="n">
+        <v>28500000</v>
+      </c>
+      <c r="X5" s="5" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="Y5" s="5" t="n">
         <v>30000000</v>
       </c>
-      <c r="P5" s="5" t="n">
-        <v>33000000</v>
-      </c>
-      <c r="Q5" s="5" t="n">
-        <v>36000000</v>
-      </c>
-      <c r="R5" s="5" t="n">
-        <v>39000000</v>
-      </c>
-      <c r="S5" s="5" t="n">
-        <v>42500000</v>
-      </c>
-      <c r="T5" s="5" t="n">
-        <v>46000000</v>
-      </c>
-      <c r="U5" s="5" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="V5" s="5" t="n">
-        <v>54000000</v>
-      </c>
-      <c r="W5" s="5" t="n">
-        <v>58000000</v>
-      </c>
-      <c r="X5" s="5" t="n">
-        <v>62000000</v>
-      </c>
-      <c r="Y5" s="5" t="n">
-        <v>66000000</v>
-      </c>
       <c r="Z5" s="6" t="n">
-        <v>720500000</v>
+        <v>431500000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Chakana savdo</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>20500000</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>24500000</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>26000000</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>30500000</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>33500000</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>36500000</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>39500000</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>41000000</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>42500000</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>44000000</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>45500000</v>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="V6" s="5" t="n">
+        <v>48500000</v>
+      </c>
+      <c r="W6" s="5" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="X6" s="5" t="n">
+        <v>51500000</v>
+      </c>
+      <c r="Y6" s="5" t="n">
+        <v>53000000</v>
+      </c>
+      <c r="Z6" s="6" t="n">
+        <v>861500000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Qulupnay</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5" t="n">
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
         <v>6187500</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F7" s="5" t="n">
         <v>12375000</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G7" s="5" t="n">
         <v>18562500</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H7" s="5" t="n">
         <v>24750000</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>24750000</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J7" s="5" t="n">
         <v>24750000</v>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="K7" s="5" t="n">
         <v>24750000</v>
       </c>
-      <c r="L6" s="5" t="n">
+      <c r="L7" s="5" t="n">
         <v>24750000</v>
       </c>
-      <c r="M6" s="5" t="n">
+      <c r="M7" s="5" t="n">
         <v>24750000</v>
       </c>
-      <c r="N6" s="5" t="n">
+      <c r="N7" s="5" t="n">
         <v>24750000</v>
       </c>
-      <c r="O6" s="5" t="n">
+      <c r="O7" s="5" t="n">
         <v>24750000</v>
       </c>
-      <c r="P6" s="5" t="n">
+      <c r="P7" s="5" t="n">
         <v>24750000</v>
       </c>
-      <c r="Q6" s="5" t="n">
+      <c r="Q7" s="5" t="n">
         <v>24750000</v>
       </c>
-      <c r="R6" s="5" t="n">
+      <c r="R7" s="5" t="n">
         <v>24750000</v>
       </c>
-      <c r="S6" s="5" t="n">
+      <c r="S7" s="5" t="n">
         <v>24750000</v>
       </c>
-      <c r="T6" s="5" t="n">
+      <c r="T7" s="5" t="n">
         <v>24750000</v>
       </c>
-      <c r="U6" s="5" t="n">
+      <c r="U7" s="5" t="n">
         <v>24750000</v>
       </c>
-      <c r="V6" s="5" t="n">
+      <c r="V7" s="5" t="n">
         <v>24750000</v>
       </c>
-      <c r="W6" s="5" t="n">
+      <c r="W7" s="5" t="n">
         <v>24750000</v>
       </c>
-      <c r="X6" s="5" t="n">
+      <c r="X7" s="5" t="n">
         <v>24750000</v>
       </c>
-      <c r="Y6" s="5" t="n">
+      <c r="Y7" s="5" t="n">
         <v>24750000</v>
       </c>
-      <c r="Z6" s="6" t="n">
+      <c r="Z7" s="6" t="n">
         <v>482625000</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>JAMI DAROMAD</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>20500000</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>24000000</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>33687500</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>43875000</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>54062500</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>64250000</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>68750000</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>73250000</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>77750000</v>
-      </c>
-      <c r="L7" s="8" t="n">
-        <v>82250000</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>87250000</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>92250000</v>
-      </c>
-      <c r="O7" s="8" t="n">
-        <v>97250000</v>
-      </c>
-      <c r="P7" s="8" t="n">
-        <v>102750000</v>
-      </c>
-      <c r="Q7" s="8" t="n">
-        <v>110750000</v>
-      </c>
-      <c r="R7" s="8" t="n">
-        <v>116250000</v>
-      </c>
-      <c r="S7" s="8" t="n">
-        <v>122250000</v>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v>130750000</v>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v>137250000</v>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v>143750000</v>
-      </c>
-      <c r="W7" s="8" t="n">
-        <v>152750000</v>
-      </c>
-      <c r="X7" s="8" t="n">
-        <v>159250000</v>
-      </c>
-      <c r="Y7" s="8" t="n">
-        <v>165750000</v>
-      </c>
-      <c r="Z7" s="6" t="n">
-        <v>2180625000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MRR (obuna)</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>20500000</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>24000000</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>31500000</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>35500000</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>39500000</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>44000000</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>48500000</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>53000000</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>57500000</v>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v>62500000</v>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v>67500000</v>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v>72500000</v>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v>78000000</v>
-      </c>
-      <c r="Q9" s="5" t="n">
-        <v>86000000</v>
-      </c>
-      <c r="R9" s="5" t="n">
-        <v>91500000</v>
-      </c>
-      <c r="S9" s="5" t="n">
-        <v>97500000</v>
-      </c>
-      <c r="T9" s="5" t="n">
-        <v>106000000</v>
-      </c>
-      <c r="U9" s="5" t="n">
-        <v>112500000</v>
-      </c>
-      <c r="V9" s="5" t="n">
-        <v>119000000</v>
-      </c>
-      <c r="W9" s="5" t="n">
-        <v>128000000</v>
-      </c>
-      <c r="X9" s="5" t="n">
-        <v>134500000</v>
-      </c>
-      <c r="Y9" s="5" t="n">
-        <v>141000000</v>
-      </c>
-      <c r="Z9" s="6" t="n">
-        <v>141000000</v>
+      <c r="B8" s="8" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>41000000</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>43500000</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>52187500</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>61875000</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>71562500</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>81250000</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>84750000</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>88250000</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>91750000</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>95250000</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>98750000</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>102250000</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>105750000</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>109250000</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>112750000</v>
+      </c>
+      <c r="R8" s="8" t="n">
+        <v>116750000</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>120750000</v>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v>124250000</v>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v>127750000</v>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v>131750000</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>135250000</v>
+      </c>
+      <c r="X8" s="8" t="n">
+        <v>138250000</v>
+      </c>
+      <c r="Y8" s="8" t="n">
+        <v>142750000</v>
+      </c>
+      <c r="Z8" s="6" t="n">
+        <v>2317625000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARR (yillik)</t>
+          <t>MRR (takrorlanuvchi)</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>240000000</v>
+        <v>19500000</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>246000000</v>
+        <v>20000000</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>288000000</v>
+        <v>21500000</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>330000000</v>
+        <v>23000000</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>378000000</v>
+        <v>25000000</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>426000000</v>
+        <v>27000000</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>474000000</v>
+        <v>29000000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>528000000</v>
+        <v>31000000</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>582000000</v>
+        <v>33000000</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>636000000</v>
+        <v>35000000</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>690000000</v>
+        <v>37000000</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>750000000</v>
+        <v>39000000</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>810000000</v>
+        <v>41000000</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>870000000</v>
+        <v>43000000</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>936000000</v>
+        <v>45000000</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>1032000000</v>
+        <v>47000000</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>1098000000</v>
+        <v>49500000</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>1170000000</v>
+        <v>52000000</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>1272000000</v>
+        <v>54000000</v>
       </c>
       <c r="U10" s="5" t="n">
-        <v>1350000000</v>
+        <v>56000000</v>
       </c>
       <c r="V10" s="5" t="n">
-        <v>1428000000</v>
+        <v>58500000</v>
       </c>
       <c r="W10" s="5" t="n">
-        <v>1536000000</v>
+        <v>60500000</v>
       </c>
       <c r="X10" s="5" t="n">
-        <v>1614000000</v>
+        <v>62000000</v>
       </c>
       <c r="Y10" s="5" t="n">
-        <v>1692000000</v>
+        <v>65000000</v>
       </c>
       <c r="Z10" s="6" t="n">
-        <v>1692000000</v>
+        <v>65000000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARPU</t>
+          <t>ARR (yillik)</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1000000</v>
+        <v>234000000</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>976190</v>
+        <v>240000000</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1000000</v>
+        <v>258000000</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1247685</v>
+        <v>276000000</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1415323</v>
+        <v>300000000</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1544643</v>
+        <v>324000000</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>1647436</v>
+        <v>348000000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>1562500</v>
+        <v>372000000</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>1494898</v>
+        <v>396000000</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>1439815</v>
+        <v>420000000</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>1394068</v>
+        <v>444000000</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>1342308</v>
+        <v>468000000</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>1299296</v>
+        <v>492000000</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>1262987</v>
+        <v>516000000</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>1223214</v>
+        <v>540000000</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>1203804</v>
+        <v>564000000</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>1174242</v>
+        <v>594000000</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>1142523</v>
+        <v>624000000</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>1127155</v>
+        <v>648000000</v>
       </c>
       <c r="U11" s="5" t="n">
-        <v>1098000</v>
+        <v>672000000</v>
       </c>
       <c r="V11" s="5" t="n">
-        <v>1072761</v>
+        <v>702000000</v>
       </c>
       <c r="W11" s="5" t="n">
-        <v>1060764</v>
+        <v>726000000</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>1040850</v>
+        <v>744000000</v>
       </c>
       <c r="Y11" s="5" t="n">
-        <v>1023148</v>
+        <v>780000000</v>
       </c>
       <c r="Z11" s="6" t="n">
-        <v>1023148</v>
+        <v>780000000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>ARPU</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1481481</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1464286</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1630859</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1767857</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1883224</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1981707</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1926136</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>1877660</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>1835000</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>1797170</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>1763393</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>1733051</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>1705645</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>1680769</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>1658088</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>1621528</v>
+      </c>
+      <c r="S12" s="5" t="n">
+        <v>1588816</v>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>1572785</v>
+      </c>
+      <c r="U12" s="5" t="n">
+        <v>1557927</v>
+      </c>
+      <c r="V12" s="5" t="n">
+        <v>1531977</v>
+      </c>
+      <c r="W12" s="5" t="n">
+        <v>1519663</v>
+      </c>
+      <c r="X12" s="5" t="n">
+        <v>1519231</v>
+      </c>
+      <c r="Y12" s="5" t="n">
+        <v>1502632</v>
+      </c>
+      <c r="Z12" s="6" t="n">
+        <v>1502632</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Daromad ($)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>1538</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>1577</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>1846</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>2591</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>3375</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>4159</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>4942</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>5288</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>5635</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>5981</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>6327</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>6712</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>7096</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>7481</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>7904</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>8519</v>
-      </c>
-      <c r="R12" s="5" t="n">
-        <v>8942</v>
-      </c>
-      <c r="S12" s="5" t="n">
-        <v>9404</v>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>10058</v>
-      </c>
-      <c r="U12" s="5" t="n">
-        <v>10558</v>
-      </c>
-      <c r="V12" s="5" t="n">
-        <v>11058</v>
-      </c>
-      <c r="W12" s="5" t="n">
-        <v>11750</v>
-      </c>
-      <c r="X12" s="5" t="n">
-        <v>12250</v>
-      </c>
-      <c r="Y12" s="5" t="n">
-        <v>12750</v>
-      </c>
-      <c r="Z12" s="6" t="n">
-        <v>167740</v>
+      <c r="B13" s="5" t="n">
+        <v>3077</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>3154</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3346</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>4014</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>4760</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>5505</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>6250</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>6519</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>6788</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>7058</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>7327</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>7596</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>7865</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>8135</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>8404</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>8673</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>8981</v>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>9288</v>
+      </c>
+      <c r="T13" s="5" t="n">
+        <v>9558</v>
+      </c>
+      <c r="U13" s="5" t="n">
+        <v>9827</v>
+      </c>
+      <c r="V13" s="5" t="n">
+        <v>10135</v>
+      </c>
+      <c r="W13" s="5" t="n">
+        <v>10404</v>
+      </c>
+      <c r="X13" s="5" t="n">
+        <v>10635</v>
+      </c>
+      <c r="Y13" s="5" t="n">
+        <v>10981</v>
+      </c>
+      <c r="Z13" s="6" t="n">
+        <v>178279</v>
       </c>
     </row>
   </sheetData>
@@ -2224,79 +2406,79 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>3000000</v>
+        <v>6000000</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>3000000</v>
+        <v>6000000</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>3000000</v>
+        <v>6000000</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="U4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="V4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="W4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="X4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>8000000</v>
+        <v>10000000</v>
       </c>
       <c r="Z4" s="6" t="n">
-        <v>177000000</v>
+        <v>228000000</v>
       </c>
     </row>
     <row r="5">
@@ -2306,79 +2488,79 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1800000</v>
+        <v>3000000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>1800000</v>
+        <v>3000000</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>1800000</v>
+        <v>3000000</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>1800000</v>
+        <v>3000000</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>1800000</v>
+        <v>3000000</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>1800000</v>
+        <v>3000000</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>1800000</v>
+        <v>3000000</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>1800000</v>
+        <v>3000000</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>1800000</v>
+        <v>3000000</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>1800000</v>
+        <v>3000000</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>1800000</v>
+        <v>3000000</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>1800000</v>
+        <v>3000000</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>1800000</v>
+        <v>3000000</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>1800000</v>
+        <v>3000000</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>1800000</v>
+        <v>3000000</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>1800000</v>
+        <v>3000000</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>1800000</v>
+        <v>3000000</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>1800000</v>
+        <v>3000000</v>
       </c>
       <c r="Z5" s="6" t="n">
-        <v>38400000</v>
+        <v>66000000</v>
       </c>
     </row>
     <row r="6">
@@ -2388,79 +2570,79 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="U6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="V6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="W6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="X6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="Y6" s="5" t="n">
-        <v>4300000</v>
+        <v>6000000</v>
       </c>
       <c r="Z6" s="6" t="n">
-        <v>94800000</v>
+        <v>135000000</v>
       </c>
     </row>
     <row r="7">
@@ -2470,79 +2652,79 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="U7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>2500000</v>
+        <v>3500000</v>
       </c>
       <c r="Z7" s="6" t="n">
-        <v>54900000</v>
+        <v>79500000</v>
       </c>
     </row>
     <row r="8">
@@ -2561,70 +2743,70 @@
         <v>1500000</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="U8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="V8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="X8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="Y8" s="5" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="Z8" s="6" t="n">
-        <v>25500000</v>
+        <v>46500000</v>
       </c>
     </row>
     <row r="9">
@@ -2634,79 +2816,79 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="V9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="W9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="Z9" s="6" t="n">
-        <v>17700000</v>
+        <v>46500000</v>
       </c>
     </row>
     <row r="10">
@@ -2716,79 +2898,79 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="U10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="V10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="W10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="X10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="Y10" s="5" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="Z10" s="6" t="n">
-        <v>11100000</v>
+        <v>18300000</v>
       </c>
     </row>
     <row r="11">
@@ -2798,79 +2980,79 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>800000</v>
+        <v>1600000</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>820000</v>
+        <v>1640000</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>960000</v>
+        <v>1740000</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1347500</v>
+        <v>2087500</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1755000</v>
+        <v>2475000</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>2162500</v>
+        <v>2862500</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>2570000</v>
+        <v>3250000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>2750000</v>
+        <v>3390000</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>2930000</v>
+        <v>3530000</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>3110000</v>
+        <v>3670000</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>3290000</v>
+        <v>3810000</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>3490000</v>
+        <v>3950000</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>3690000</v>
+        <v>4090000</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>3890000</v>
+        <v>4230000</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>4110000</v>
+        <v>4370000</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>4430000</v>
+        <v>4510000</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>4650000</v>
+        <v>4670000</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>4890000</v>
+        <v>4830000</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>5230000</v>
+        <v>4970000</v>
       </c>
       <c r="U11" s="5" t="n">
-        <v>5490000</v>
+        <v>5110000</v>
       </c>
       <c r="V11" s="5" t="n">
-        <v>5750000</v>
+        <v>5270000</v>
       </c>
       <c r="W11" s="5" t="n">
-        <v>6110000</v>
+        <v>5410000</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>6370000</v>
+        <v>5530000</v>
       </c>
       <c r="Y11" s="5" t="n">
-        <v>6630000</v>
+        <v>5710000</v>
       </c>
       <c r="Z11" s="6" t="n">
-        <v>87225000</v>
+        <v>92705000</v>
       </c>
     </row>
     <row r="12">
@@ -2880,79 +3062,79 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>9100000</v>
+        <v>18100000</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>9120000</v>
+        <v>18140000</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>9260000</v>
+        <v>18240000</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>19447500</v>
+        <v>28387500</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>19855000</v>
+        <v>28775000</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>20262500</v>
+        <v>29162500</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>21470000</v>
+        <v>30550000</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>21650000</v>
+        <v>30690000</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>21830000</v>
+        <v>30830000</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>22010000</v>
+        <v>30970000</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>22190000</v>
+        <v>31110000</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>22390000</v>
+        <v>31250000</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>22590000</v>
+        <v>31390000</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>22790000</v>
+        <v>31530000</v>
       </c>
       <c r="P12" s="8" t="n">
-        <v>23010000</v>
+        <v>31670000</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>23330000</v>
+        <v>31810000</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>23550000</v>
+        <v>31970000</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>23790000</v>
+        <v>32130000</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>24130000</v>
+        <v>32270000</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>24390000</v>
+        <v>32410000</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>24650000</v>
+        <v>32570000</v>
       </c>
       <c r="W12" s="8" t="n">
-        <v>25010000</v>
+        <v>32710000</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>25270000</v>
+        <v>32830000</v>
       </c>
       <c r="Y12" s="8" t="n">
-        <v>25530000</v>
+        <v>33010000</v>
       </c>
       <c r="Z12" s="6" t="n">
-        <v>506625000</v>
+        <v>712505000</v>
       </c>
     </row>
     <row r="14">
@@ -2962,79 +3144,79 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>6000000</v>
+        <v>12000000</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>6150000</v>
+        <v>12300000</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>7200000</v>
+        <v>13050000</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>11034375</v>
+        <v>16584375</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>15018750</v>
+        <v>20418750</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>19003125</v>
+        <v>24253125</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>22987500</v>
+        <v>28087500</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>24337500</v>
+        <v>29137500</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>25687500</v>
+        <v>30187500</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>27037500</v>
+        <v>31237500</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>28387500</v>
+        <v>32287500</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>29887500</v>
+        <v>33337500</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>31387500</v>
+        <v>34387500</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>32887500</v>
+        <v>35437500</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>34537500</v>
+        <v>36487500</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>36937500</v>
+        <v>37537500</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>38587500</v>
+        <v>38737500</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>40387500</v>
+        <v>39937500</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>42937500</v>
+        <v>40987500</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>44887500</v>
+        <v>42037500</v>
       </c>
       <c r="V14" s="5" t="n">
-        <v>46837500</v>
+        <v>43237500</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>49537500</v>
+        <v>44287500</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>51487500</v>
+        <v>45187500</v>
       </c>
       <c r="Y14" s="5" t="n">
-        <v>53437500</v>
+        <v>46537500</v>
       </c>
       <c r="Z14" s="6" t="n">
-        <v>726581250</v>
+        <v>767681250</v>
       </c>
     </row>
     <row r="15">
@@ -3044,79 +3226,79 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>14000000</v>
+        <v>28000000</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>14350000</v>
+        <v>28700000</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>16800000</v>
+        <v>30450000</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>22653125</v>
+        <v>35603125</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>28856250</v>
+        <v>41456250</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>35059375</v>
+        <v>47309375</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>41262500</v>
+        <v>53162500</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>44412500</v>
+        <v>55612500</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>47562500</v>
+        <v>58062500</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>50712500</v>
+        <v>60512500</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>53862500</v>
+        <v>62962500</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>57362500</v>
+        <v>65412500</v>
       </c>
       <c r="N15" s="8" t="n">
-        <v>60862500</v>
+        <v>67862500</v>
       </c>
       <c r="O15" s="8" t="n">
-        <v>64362500</v>
+        <v>70312500</v>
       </c>
       <c r="P15" s="8" t="n">
-        <v>68212500</v>
+        <v>72762500</v>
       </c>
       <c r="Q15" s="8" t="n">
-        <v>73812500</v>
+        <v>75212500</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>77662500</v>
+        <v>78012500</v>
       </c>
       <c r="S15" s="8" t="n">
-        <v>81862500</v>
+        <v>80812500</v>
       </c>
       <c r="T15" s="8" t="n">
-        <v>87812500</v>
+        <v>83262500</v>
       </c>
       <c r="U15" s="8" t="n">
-        <v>92362500</v>
+        <v>85712500</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>96912500</v>
+        <v>88512500</v>
       </c>
       <c r="W15" s="8" t="n">
-        <v>103212500</v>
+        <v>90962500</v>
       </c>
       <c r="X15" s="8" t="n">
-        <v>107762500</v>
+        <v>93062500</v>
       </c>
       <c r="Y15" s="8" t="n">
-        <v>112312500</v>
+        <v>96212500</v>
       </c>
       <c r="Z15" s="6" t="n">
-        <v>1454043750</v>
+        <v>1549943750</v>
       </c>
     </row>
     <row r="16">
@@ -3135,70 +3317,70 @@
         <v>70</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>67.2</v>
+        <v>68.2</v>
       </c>
       <c r="F16" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="J16" s="9" t="n">
         <v>65.8</v>
       </c>
-      <c r="G16" s="9" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>64.90000000000001</v>
-      </c>
       <c r="K16" s="9" t="n">
-        <v>65.2</v>
+        <v>66</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>65.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>65.7</v>
+        <v>66.2</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>66</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>66.2</v>
+        <v>66.5</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>66.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>66.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="R16" s="9" t="n">
         <v>66.8</v>
       </c>
       <c r="S16" s="9" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="T16" s="9" t="n">
         <v>67</v>
       </c>
-      <c r="T16" s="9" t="n">
+      <c r="U16" s="9" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="V16" s="9" t="n">
         <v>67.2</v>
       </c>
-      <c r="U16" s="9" t="n">
+      <c r="W16" s="9" t="n">
         <v>67.3</v>
       </c>
-      <c r="V16" s="9" t="n">
+      <c r="X16" s="9" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="Y16" s="9" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="W16" s="9" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="X16" s="9" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="Y16" s="9" t="n">
-        <v>67.8</v>
-      </c>
       <c r="Z16" s="10" t="n">
-        <v>66.7</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3474,79 +3656,79 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>20000000</v>
+        <v>40000000</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>20500000</v>
+        <v>41000000</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>24000000</v>
+        <v>43500000</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>33687500</v>
+        <v>52187500</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>43875000</v>
+        <v>61875000</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>54062500</v>
+        <v>71562500</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>64250000</v>
+        <v>81250000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>68750000</v>
+        <v>84750000</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>73250000</v>
+        <v>88250000</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>77750000</v>
+        <v>91750000</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>82250000</v>
+        <v>95250000</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>87250000</v>
+        <v>98750000</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>92250000</v>
+        <v>102250000</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>97250000</v>
+        <v>105750000</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>102750000</v>
+        <v>109250000</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>110750000</v>
+        <v>112750000</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>116250000</v>
+        <v>116750000</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>122250000</v>
+        <v>120750000</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>130750000</v>
+        <v>124250000</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>137250000</v>
+        <v>127750000</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>143750000</v>
+        <v>131750000</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>152750000</v>
+        <v>135250000</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>159250000</v>
+        <v>138250000</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>165750000</v>
+        <v>142750000</v>
       </c>
       <c r="Z5" s="6" t="n">
-        <v>2180625000</v>
+        <v>2317625000</v>
       </c>
     </row>
     <row r="6">
@@ -3556,79 +3738,79 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>475000000</v>
+        <v>495000000</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>20500000</v>
+        <v>41000000</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>24000000</v>
+        <v>43500000</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>33687500</v>
+        <v>52187500</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>43875000</v>
+        <v>61875000</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>54062500</v>
+        <v>71562500</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>64250000</v>
+        <v>81250000</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>68750000</v>
+        <v>84750000</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>73250000</v>
+        <v>88250000</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>77750000</v>
+        <v>91750000</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>82250000</v>
+        <v>95250000</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>87250000</v>
+        <v>98750000</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>92250000</v>
+        <v>102250000</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>97250000</v>
+        <v>105750000</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>102750000</v>
+        <v>109250000</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>110750000</v>
+        <v>112750000</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>116250000</v>
+        <v>116750000</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>122250000</v>
+        <v>120750000</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>130750000</v>
+        <v>124250000</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>137250000</v>
+        <v>127750000</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>143750000</v>
+        <v>131750000</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>152750000</v>
+        <v>135250000</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>159250000</v>
+        <v>138250000</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>165750000</v>
+        <v>142750000</v>
       </c>
       <c r="Z6" s="6" t="n">
-        <v>2635625000</v>
+        <v>2772625000</v>
       </c>
     </row>
     <row r="8">
@@ -3802,79 +3984,79 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>9100000</v>
+        <v>18100000</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>9120000</v>
+        <v>18140000</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>9260000</v>
+        <v>18240000</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>19447500</v>
+        <v>28387500</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>19855000</v>
+        <v>28775000</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>20262500</v>
+        <v>29162500</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>21470000</v>
+        <v>30550000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>21650000</v>
+        <v>30690000</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>21830000</v>
+        <v>30830000</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>22010000</v>
+        <v>30970000</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>22190000</v>
+        <v>31110000</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>22390000</v>
+        <v>31250000</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>22590000</v>
+        <v>31390000</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>22790000</v>
+        <v>31530000</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>23010000</v>
+        <v>31670000</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>23330000</v>
+        <v>31810000</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>23550000</v>
+        <v>31970000</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>23790000</v>
+        <v>32130000</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>24130000</v>
+        <v>32270000</v>
       </c>
       <c r="U10" s="5" t="n">
-        <v>24390000</v>
+        <v>32410000</v>
       </c>
       <c r="V10" s="5" t="n">
-        <v>24650000</v>
+        <v>32570000</v>
       </c>
       <c r="W10" s="5" t="n">
-        <v>25010000</v>
+        <v>32710000</v>
       </c>
       <c r="X10" s="5" t="n">
-        <v>25270000</v>
+        <v>32830000</v>
       </c>
       <c r="Y10" s="5" t="n">
-        <v>25530000</v>
+        <v>33010000</v>
       </c>
       <c r="Z10" s="6" t="n">
-        <v>506625000</v>
+        <v>712505000</v>
       </c>
     </row>
     <row r="11">
@@ -3884,79 +4066,79 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>266669000</v>
+        <v>275669000</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>9120000</v>
+        <v>18140000</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>9260000</v>
+        <v>18240000</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>19447500</v>
+        <v>28387500</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>19855000</v>
+        <v>28775000</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>20262500</v>
+        <v>29162500</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>21470000</v>
+        <v>30550000</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>21650000</v>
+        <v>30690000</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>21830000</v>
+        <v>30830000</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>22010000</v>
+        <v>30970000</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>22190000</v>
+        <v>31110000</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>22390000</v>
+        <v>31250000</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>22590000</v>
+        <v>31390000</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>22790000</v>
+        <v>31530000</v>
       </c>
       <c r="P11" s="8" t="n">
-        <v>23010000</v>
+        <v>31670000</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>23330000</v>
+        <v>31810000</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>23550000</v>
+        <v>31970000</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>23790000</v>
+        <v>32130000</v>
       </c>
       <c r="T11" s="8" t="n">
-        <v>24130000</v>
+        <v>32270000</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>24390000</v>
+        <v>32410000</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>24650000</v>
+        <v>32570000</v>
       </c>
       <c r="W11" s="8" t="n">
-        <v>25010000</v>
+        <v>32710000</v>
       </c>
       <c r="X11" s="8" t="n">
-        <v>25270000</v>
+        <v>32830000</v>
       </c>
       <c r="Y11" s="8" t="n">
-        <v>25530000</v>
+        <v>33010000</v>
       </c>
       <c r="Z11" s="6" t="n">
-        <v>764194000</v>
+        <v>970074000</v>
       </c>
     </row>
     <row r="13">
@@ -3966,79 +4148,79 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>208331000</v>
+        <v>219331000</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>11380000</v>
+        <v>22860000</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>14740000</v>
+        <v>25260000</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>14240000</v>
+        <v>23800000</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>24020000</v>
+        <v>33100000</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>33800000</v>
+        <v>42400000</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>42780000</v>
+        <v>50700000</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>47100000</v>
+        <v>54060000</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>51420000</v>
+        <v>57420000</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>55740000</v>
+        <v>60780000</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>60060000</v>
+        <v>64140000</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>64860000</v>
+        <v>67500000</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>69660000</v>
+        <v>70860000</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>74460000</v>
+        <v>74220000</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>79740000</v>
+        <v>77580000</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>87420000</v>
+        <v>80940000</v>
       </c>
       <c r="R13" s="8" t="n">
-        <v>92700000</v>
+        <v>84780000</v>
       </c>
       <c r="S13" s="8" t="n">
-        <v>98460000</v>
+        <v>88620000</v>
       </c>
       <c r="T13" s="8" t="n">
-        <v>106620000</v>
+        <v>91980000</v>
       </c>
       <c r="U13" s="8" t="n">
-        <v>112860000</v>
+        <v>95340000</v>
       </c>
       <c r="V13" s="8" t="n">
-        <v>119100000</v>
+        <v>99180000</v>
       </c>
       <c r="W13" s="8" t="n">
-        <v>127740000</v>
+        <v>102540000</v>
       </c>
       <c r="X13" s="8" t="n">
-        <v>133980000</v>
+        <v>105420000</v>
       </c>
       <c r="Y13" s="8" t="n">
-        <v>140220000</v>
+        <v>109740000</v>
       </c>
       <c r="Z13" s="6" t="n">
-        <v>1871431000</v>
+        <v>1802551000</v>
       </c>
     </row>
     <row r="14">
@@ -4048,79 +4230,79 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>213331000</v>
+        <v>224331000</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>224711000</v>
+        <v>247191000</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>239451000</v>
+        <v>272451000</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>253691000</v>
+        <v>296251000</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>277711000</v>
+        <v>329351000</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>311511000</v>
+        <v>371751000</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>354291000</v>
+        <v>422451000</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>401391000</v>
+        <v>476511000</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>452811000</v>
+        <v>533931000</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>508551000</v>
+        <v>594711000</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>568611000</v>
+        <v>658851000</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>633471000</v>
+        <v>726351000</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>703131000</v>
+        <v>797211000</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>777591000</v>
+        <v>871431000</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>857331000</v>
+        <v>949011000</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>944751000</v>
+        <v>1029951000</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>1037451000</v>
+        <v>1114731000</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>1135911000</v>
+        <v>1203351000</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>1242531000</v>
+        <v>1295331000</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>1355391000</v>
+        <v>1390671000</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>1474491000</v>
+        <v>1489851000</v>
       </c>
       <c r="W14" s="8" t="n">
-        <v>1602231000</v>
+        <v>1592391000</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>1736211000</v>
+        <v>1697811000</v>
       </c>
       <c r="Y14" s="8" t="n">
-        <v>1876431000</v>
+        <v>1807551000</v>
       </c>
       <c r="Z14" s="6" t="n">
-        <v>1876431000</v>
+        <v>1807551000</v>
       </c>
     </row>
   </sheetData>
@@ -4314,79 +4496,79 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>20000000</v>
+        <v>40000000</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>20500000</v>
+        <v>41000000</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>24000000</v>
+        <v>43500000</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>33687500</v>
+        <v>52187500</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>43875000</v>
+        <v>61875000</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>54062500</v>
+        <v>71562500</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>64250000</v>
+        <v>81250000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>68750000</v>
+        <v>84750000</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>73250000</v>
+        <v>88250000</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>77750000</v>
+        <v>91750000</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>82250000</v>
+        <v>95250000</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>87250000</v>
+        <v>98750000</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>92250000</v>
+        <v>102250000</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>97250000</v>
+        <v>105750000</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>102750000</v>
+        <v>109250000</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>110750000</v>
+        <v>112750000</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>116250000</v>
+        <v>116750000</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>122250000</v>
+        <v>120750000</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>130750000</v>
+        <v>124250000</v>
       </c>
       <c r="U4" s="5" t="n">
-        <v>137250000</v>
+        <v>127750000</v>
       </c>
       <c r="V4" s="5" t="n">
-        <v>143750000</v>
+        <v>131750000</v>
       </c>
       <c r="W4" s="5" t="n">
-        <v>152750000</v>
+        <v>135250000</v>
       </c>
       <c r="X4" s="5" t="n">
-        <v>159250000</v>
+        <v>138250000</v>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>165750000</v>
+        <v>142750000</v>
       </c>
       <c r="Z4" s="6" t="n">
-        <v>2180625000</v>
+        <v>2317625000</v>
       </c>
     </row>
     <row r="5">
@@ -4396,79 +4578,79 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>6000000</v>
+        <v>12000000</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>6150000</v>
+        <v>12300000</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>7200000</v>
+        <v>13050000</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>11034375</v>
+        <v>16584375</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>15018750</v>
+        <v>20418750</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>19003125</v>
+        <v>24253125</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>22987500</v>
+        <v>28087500</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>24337500</v>
+        <v>29137500</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>25687500</v>
+        <v>30187500</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>27037500</v>
+        <v>31237500</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>28387500</v>
+        <v>32287500</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>29887500</v>
+        <v>33337500</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>31387500</v>
+        <v>34387500</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>32887500</v>
+        <v>35437500</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>34537500</v>
+        <v>36487500</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>36937500</v>
+        <v>37537500</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>38587500</v>
+        <v>38737500</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>40387500</v>
+        <v>39937500</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>42937500</v>
+        <v>40987500</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>44887500</v>
+        <v>42037500</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>46837500</v>
+        <v>43237500</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>49537500</v>
+        <v>44287500</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>51487500</v>
+        <v>45187500</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>53437500</v>
+        <v>46537500</v>
       </c>
       <c r="Z5" s="6" t="n">
-        <v>726581250</v>
+        <v>767681250</v>
       </c>
     </row>
     <row r="6">
@@ -4478,79 +4660,79 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>14000000</v>
+        <v>28000000</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>14350000</v>
+        <v>28700000</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>16800000</v>
+        <v>30450000</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>22653125</v>
+        <v>35603125</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>28856250</v>
+        <v>41456250</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>35059375</v>
+        <v>47309375</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>41262500</v>
+        <v>53162500</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>44412500</v>
+        <v>55612500</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>47562500</v>
+        <v>58062500</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>50712500</v>
+        <v>60512500</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>53862500</v>
+        <v>62962500</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>57362500</v>
+        <v>65412500</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>60862500</v>
+        <v>67862500</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>64362500</v>
+        <v>70312500</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>68212500</v>
+        <v>72762500</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>73812500</v>
+        <v>75212500</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>77662500</v>
+        <v>78012500</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>81862500</v>
+        <v>80812500</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>87812500</v>
+        <v>83262500</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>92362500</v>
+        <v>85712500</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>96912500</v>
+        <v>88512500</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>103212500</v>
+        <v>90962500</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>107762500</v>
+        <v>93062500</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>112312500</v>
+        <v>96212500</v>
       </c>
       <c r="Z6" s="6" t="n">
-        <v>1454043750</v>
+        <v>1549943750</v>
       </c>
     </row>
     <row r="7">
@@ -4560,79 +4742,79 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>8300000</v>
+        <v>16500000</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>8300000</v>
+        <v>16500000</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>8300000</v>
+        <v>16500000</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>18100000</v>
+        <v>26300000</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>18100000</v>
+        <v>26300000</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>18100000</v>
+        <v>26300000</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>18900000</v>
+        <v>27300000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>18900000</v>
+        <v>27300000</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>18900000</v>
+        <v>27300000</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>18900000</v>
+        <v>27300000</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>18900000</v>
+        <v>27300000</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>18900000</v>
+        <v>27300000</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>18900000</v>
+        <v>27300000</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>18900000</v>
+        <v>27300000</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>18900000</v>
+        <v>27300000</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>18900000</v>
+        <v>27300000</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>18900000</v>
+        <v>27300000</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>18900000</v>
+        <v>27300000</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>18900000</v>
+        <v>27300000</v>
       </c>
       <c r="U7" s="5" t="n">
-        <v>18900000</v>
+        <v>27300000</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>18900000</v>
+        <v>27300000</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>18900000</v>
+        <v>27300000</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>18900000</v>
+        <v>27300000</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>18900000</v>
+        <v>27300000</v>
       </c>
       <c r="Z7" s="6" t="n">
-        <v>419400000</v>
+        <v>619800000</v>
       </c>
     </row>
     <row r="8">
@@ -4642,79 +4824,79 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>5700000</v>
+        <v>11500000</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>6050000</v>
+        <v>12200000</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>8500000</v>
+        <v>13950000</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>4553125</v>
+        <v>9303125</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>10756250</v>
+        <v>15156250</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>16959375</v>
+        <v>21009375</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>22362500</v>
+        <v>25862500</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>25512500</v>
+        <v>28312500</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>28662500</v>
+        <v>30762500</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>31812500</v>
+        <v>33212500</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>34962500</v>
+        <v>35662500</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>38462500</v>
+        <v>38112500</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>41962500</v>
+        <v>40562500</v>
       </c>
       <c r="O8" s="8" t="n">
+        <v>43012500</v>
+      </c>
+      <c r="P8" s="8" t="n">
         <v>45462500</v>
       </c>
-      <c r="P8" s="8" t="n">
-        <v>49312500</v>
-      </c>
       <c r="Q8" s="8" t="n">
-        <v>54912500</v>
+        <v>47912500</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>58762500</v>
+        <v>50712500</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>62962500</v>
+        <v>53512500</v>
       </c>
       <c r="T8" s="8" t="n">
+        <v>55962500</v>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v>58412500</v>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v>61212500</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>63662500</v>
+      </c>
+      <c r="X8" s="8" t="n">
+        <v>65762500</v>
+      </c>
+      <c r="Y8" s="8" t="n">
         <v>68912500</v>
       </c>
-      <c r="U8" s="8" t="n">
-        <v>73462500</v>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v>78012500</v>
-      </c>
-      <c r="W8" s="8" t="n">
-        <v>84312500</v>
-      </c>
-      <c r="X8" s="8" t="n">
-        <v>88862500</v>
-      </c>
-      <c r="Y8" s="8" t="n">
-        <v>93412500</v>
-      </c>
       <c r="Z8" s="6" t="n">
-        <v>1034643750</v>
+        <v>930143750</v>
       </c>
     </row>
     <row r="9">
@@ -4724,79 +4906,79 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>800000</v>
+        <v>1600000</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>820000</v>
+        <v>1640000</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>960000</v>
+        <v>1740000</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1347500</v>
+        <v>2087500</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1755000</v>
+        <v>2475000</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>2162500</v>
+        <v>2862500</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>2570000</v>
+        <v>3250000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>2750000</v>
+        <v>3390000</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>2930000</v>
+        <v>3530000</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>3110000</v>
+        <v>3670000</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>3290000</v>
+        <v>3810000</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>3490000</v>
+        <v>3950000</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>3690000</v>
+        <v>4090000</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>3890000</v>
+        <v>4230000</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>4110000</v>
+        <v>4370000</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>4430000</v>
+        <v>4510000</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>4650000</v>
+        <v>4670000</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>4890000</v>
+        <v>4830000</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>5230000</v>
+        <v>4970000</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v>5490000</v>
+        <v>5110000</v>
       </c>
       <c r="V9" s="5" t="n">
-        <v>5750000</v>
+        <v>5270000</v>
       </c>
       <c r="W9" s="5" t="n">
-        <v>6110000</v>
+        <v>5410000</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>6370000</v>
+        <v>5530000</v>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>6630000</v>
+        <v>5710000</v>
       </c>
       <c r="Z9" s="6" t="n">
-        <v>87225000</v>
+        <v>92705000</v>
       </c>
     </row>
     <row r="10">
@@ -4806,79 +4988,79 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>4900000</v>
+        <v>9900000</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>5230000</v>
+        <v>10560000</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>7540000</v>
+        <v>12210000</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3205625</v>
+        <v>7215625</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>9001250</v>
+        <v>12681250</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>14796875</v>
+        <v>18146875</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>19792500</v>
+        <v>22612500</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>22762500</v>
+        <v>24922500</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>25732500</v>
+        <v>27232500</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>28702500</v>
+        <v>29542500</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>31672500</v>
+        <v>31852500</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>34972500</v>
+        <v>34162500</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>38272500</v>
+        <v>36472500</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>41572500</v>
+        <v>38782500</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>45202500</v>
+        <v>41092500</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>50482500</v>
+        <v>43402500</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>54112500</v>
+        <v>46042500</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>58072500</v>
+        <v>48682500</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>63682500</v>
+        <v>50992500</v>
       </c>
       <c r="U10" s="5" t="n">
-        <v>67972500</v>
+        <v>53302500</v>
       </c>
       <c r="V10" s="5" t="n">
-        <v>72262500</v>
+        <v>55942500</v>
       </c>
       <c r="W10" s="5" t="n">
-        <v>78202500</v>
+        <v>58252500</v>
       </c>
       <c r="X10" s="5" t="n">
-        <v>82492500</v>
+        <v>60232500</v>
       </c>
       <c r="Y10" s="5" t="n">
-        <v>86782500</v>
+        <v>63202500</v>
       </c>
       <c r="Z10" s="6" t="n">
-        <v>947418750</v>
+        <v>837438750</v>
       </c>
     </row>
     <row r="11">
@@ -4970,79 +5152,79 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>4900000</v>
+        <v>9900000</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>5230000</v>
+        <v>10560000</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>7540000</v>
+        <v>12210000</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>-257358</v>
+        <v>3752642</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>5538267</v>
+        <v>9218267</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>11333892</v>
+        <v>14683892</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>16329517</v>
+        <v>19149517</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>19299517</v>
+        <v>21459517</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>22269517</v>
+        <v>23769517</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>25239517</v>
+        <v>26079517</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>28209517</v>
+        <v>28389517</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>31509517</v>
+        <v>30699517</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>34809517</v>
+        <v>33009517</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>38109517</v>
+        <v>35319517</v>
       </c>
       <c r="P12" s="8" t="n">
-        <v>41739517</v>
+        <v>37629517</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>47019517</v>
+        <v>39939517</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>50649517</v>
+        <v>42579517</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>54609517</v>
+        <v>45219517</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>60219517</v>
+        <v>47529517</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>64509517</v>
+        <v>49839517</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>68799517</v>
+        <v>52479517</v>
       </c>
       <c r="W12" s="8" t="n">
-        <v>74739517</v>
+        <v>54789517</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>79029517</v>
+        <v>56769517</v>
       </c>
       <c r="Y12" s="8" t="n">
-        <v>83319517</v>
+        <v>59739517</v>
       </c>
       <c r="Z12" s="6" t="n">
-        <v>874696107</v>
+        <v>764716107</v>
       </c>
     </row>
     <row r="13">
@@ -5052,79 +5234,79 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>25.5</v>
+        <v>25.8</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>31.4</v>
+        <v>28.1</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>-0.8</v>
+        <v>7.2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>12.6</v>
+        <v>14.9</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>25.4</v>
+        <v>23.6</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>28.1</v>
+        <v>25.3</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>32.5</v>
+        <v>28.4</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>34.3</v>
+        <v>29.8</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>36.1</v>
+        <v>31.1</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>37.7</v>
+        <v>32.3</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>39.2</v>
+        <v>33.4</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>40.6</v>
+        <v>34.4</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>42.5</v>
+        <v>35.4</v>
       </c>
       <c r="R13" s="9" t="n">
-        <v>43.6</v>
+        <v>36.5</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>44.7</v>
+        <v>37.4</v>
       </c>
       <c r="T13" s="9" t="n">
-        <v>46.1</v>
+        <v>38.3</v>
       </c>
       <c r="U13" s="9" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>47.9</v>
+        <v>39.8</v>
       </c>
       <c r="W13" s="9" t="n">
-        <v>48.9</v>
+        <v>40.5</v>
       </c>
       <c r="X13" s="9" t="n">
-        <v>49.6</v>
+        <v>41.1</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>50.3</v>
+        <v>41.8</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>40.1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
@@ -5134,79 +5316,79 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>4900000</v>
+        <v>9900000</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>10130000</v>
+        <v>20460000</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>17670000</v>
+        <v>32670000</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>17412642</v>
+        <v>36422642</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>22950909</v>
+        <v>45640909</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>34284801</v>
+        <v>60324801</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>50614318</v>
+        <v>79474318</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>69913835</v>
+        <v>100933835</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>92183352</v>
+        <v>124703352</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>117422869</v>
+        <v>150782869</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>145632386</v>
+        <v>179172386</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>177141903</v>
+        <v>209871903</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>211951420</v>
+        <v>242881420</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>250060937</v>
+        <v>278200937</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>291800454</v>
+        <v>315830454</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>338819971</v>
+        <v>355769971</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>389469488</v>
+        <v>398349488</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>444079005</v>
+        <v>443569005</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>504298522</v>
+        <v>491098522</v>
       </c>
       <c r="U15" s="5" t="n">
-        <v>568808039</v>
+        <v>540938039</v>
       </c>
       <c r="V15" s="5" t="n">
-        <v>637607556</v>
+        <v>593417556</v>
       </c>
       <c r="W15" s="5" t="n">
-        <v>712347073</v>
+        <v>648207073</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>791376590</v>
+        <v>704976590</v>
       </c>
       <c r="Y15" s="5" t="n">
-        <v>874696107</v>
+        <v>764716107</v>
       </c>
       <c r="Z15" s="6" t="n">
-        <v>874696107</v>
+        <v>764716107</v>
       </c>
     </row>
   </sheetData>
@@ -5400,79 +5582,79 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="C4" s="5" t="n">
         <v>20000000</v>
       </c>
-      <c r="C4" s="5" t="n">
-        <v>20500000</v>
-      </c>
       <c r="D4" s="5" t="n">
-        <v>24000000</v>
+        <v>21500000</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>27500000</v>
+        <v>23000000</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>31500000</v>
+        <v>25000000</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>35500000</v>
+        <v>27000000</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>39500000</v>
+        <v>29000000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>44000000</v>
+        <v>31000000</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>48500000</v>
+        <v>33000000</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>53000000</v>
+        <v>35000000</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>57500000</v>
+        <v>37000000</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>62500000</v>
+        <v>39000000</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>67500000</v>
+        <v>41000000</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>72500000</v>
+        <v>43000000</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>78000000</v>
+        <v>45000000</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>86000000</v>
+        <v>47000000</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>91500000</v>
+        <v>49500000</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>97500000</v>
+        <v>52000000</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>106000000</v>
+        <v>54000000</v>
       </c>
       <c r="U4" s="5" t="n">
-        <v>112500000</v>
+        <v>56000000</v>
       </c>
       <c r="V4" s="5" t="n">
-        <v>119000000</v>
+        <v>58500000</v>
       </c>
       <c r="W4" s="5" t="n">
-        <v>128000000</v>
+        <v>60500000</v>
       </c>
       <c r="X4" s="5" t="n">
-        <v>134500000</v>
+        <v>62000000</v>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>141000000</v>
+        <v>65000000</v>
       </c>
       <c r="Z4" s="6" t="n">
-        <v>141000000</v>
+        <v>65000000</v>
       </c>
     </row>
     <row r="5">
@@ -5482,79 +5664,79 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
+        <v>234000000</v>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>240000000</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>246000000</v>
-      </c>
       <c r="D5" s="5" t="n">
-        <v>288000000</v>
+        <v>258000000</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>330000000</v>
+        <v>276000000</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>378000000</v>
+        <v>300000000</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>426000000</v>
+        <v>324000000</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>474000000</v>
+        <v>348000000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>528000000</v>
+        <v>372000000</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>582000000</v>
+        <v>396000000</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>636000000</v>
+        <v>420000000</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>690000000</v>
+        <v>444000000</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>750000000</v>
+        <v>468000000</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>810000000</v>
+        <v>492000000</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>870000000</v>
+        <v>516000000</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>936000000</v>
+        <v>540000000</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>1032000000</v>
+        <v>564000000</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>1098000000</v>
+        <v>594000000</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>1170000000</v>
+        <v>624000000</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>1272000000</v>
+        <v>648000000</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>1350000000</v>
+        <v>672000000</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>1428000000</v>
+        <v>702000000</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>1536000000</v>
+        <v>726000000</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>1614000000</v>
+        <v>744000000</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>1692000000</v>
+        <v>780000000</v>
       </c>
       <c r="Z5" s="6" t="n">
-        <v>1692000000</v>
+        <v>780000000</v>
       </c>
     </row>
     <row r="6">
@@ -5564,79 +5746,79 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1000000</v>
+        <v>1481481</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>976190</v>
+        <v>1464286</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1000000</v>
+        <v>1450000</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1247685</v>
+        <v>1630859</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1415323</v>
+        <v>1767857</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1544643</v>
+        <v>1883224</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1647436</v>
+        <v>1981707</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1562500</v>
+        <v>1926136</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>1494898</v>
+        <v>1877660</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>1439815</v>
+        <v>1835000</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>1394068</v>
+        <v>1797170</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>1342308</v>
+        <v>1763393</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>1299296</v>
+        <v>1733051</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>1262987</v>
+        <v>1705645</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>1223214</v>
+        <v>1680769</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>1203804</v>
+        <v>1658088</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>1174242</v>
+        <v>1621528</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>1142523</v>
+        <v>1588816</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>1127155</v>
+        <v>1572785</v>
       </c>
       <c r="U6" s="5" t="n">
-        <v>1098000</v>
+        <v>1557927</v>
       </c>
       <c r="V6" s="5" t="n">
-        <v>1072761</v>
+        <v>1531977</v>
       </c>
       <c r="W6" s="5" t="n">
-        <v>1060764</v>
+        <v>1519663</v>
       </c>
       <c r="X6" s="5" t="n">
-        <v>1040850</v>
+        <v>1519231</v>
       </c>
       <c r="Y6" s="5" t="n">
-        <v>1023148</v>
+        <v>1502632</v>
       </c>
       <c r="Z6" s="6" t="n">
-        <v>1241400</v>
+        <v>1668787</v>
       </c>
     </row>
     <row r="7">
@@ -5651,76 +5833,76 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>2700000</v>
+        <v>3900000</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>900000</v>
+        <v>1950000</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1400000</v>
+        <v>3000000</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1050000</v>
+        <v>2000000</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1050000</v>
+        <v>2000000</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1050000</v>
+        <v>2000000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>840000</v>
+        <v>2000000</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>840000</v>
+        <v>2000000</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>840000</v>
+        <v>2000000</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>840000</v>
+        <v>2000000</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>700000</v>
+        <v>2000000</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>700000</v>
+        <v>2000000</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>700000</v>
+        <v>2000000</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>600000</v>
+        <v>2000000</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>525000</v>
+        <v>2000000</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>600000</v>
+        <v>1500000</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>525000</v>
+        <v>1500000</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>466667</v>
+        <v>2000000</v>
       </c>
       <c r="U7" s="5" t="n">
-        <v>466667</v>
+        <v>2000000</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>466667</v>
+        <v>1500000</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>420000</v>
+        <v>2000000</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>466667</v>
+        <v>3000000</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>466667</v>
+        <v>1500000</v>
       </c>
       <c r="Z7" s="6" t="n">
-        <v>809275</v>
+        <v>2080435</v>
       </c>
     </row>
     <row r="8">
@@ -5730,79 +5912,79 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>16800000</v>
+        <v>24888881</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>16399992</v>
+        <v>24600005</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>16800000</v>
+        <v>24360000</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>20136108</v>
+        <v>26702338</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>22340329</v>
+        <v>28427141</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>24040717</v>
+        <v>29879610</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>25392309</v>
+        <v>31119507</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>24225000</v>
+        <v>30334085</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>23295919</v>
+        <v>29648943</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>22538892</v>
+        <v>29046000</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>21910173</v>
+        <v>28511324</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>21180005</v>
+        <v>28033931</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>20573243</v>
+        <v>27605087</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>20061039</v>
+        <v>27217739</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>19489281</v>
+        <v>26866150</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>19255429</v>
+        <v>26545584</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>18827266</v>
+        <v>26004170</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>18361676</v>
+        <v>25519740</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>18168101</v>
+        <v>25294940</v>
       </c>
       <c r="U8" s="5" t="n">
-        <v>17733600</v>
+        <v>25086588</v>
       </c>
       <c r="V8" s="5" t="n">
-        <v>17357460</v>
+        <v>24701167</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>17202085</v>
+        <v>24529215</v>
       </c>
       <c r="X8" s="5" t="n">
-        <v>16903927</v>
+        <v>24543960</v>
       </c>
       <c r="Y8" s="5" t="n">
-        <v>16638886</v>
+        <v>24306323</v>
       </c>
       <c r="Z8" s="6" t="n">
-        <v>19817977</v>
+        <v>26823851</v>
       </c>
     </row>
     <row r="9">
@@ -5817,76 +5999,76 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>18.7</v>
+        <v>12.5</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>14.4</v>
+        <v>8.9</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>21.3</v>
+        <v>14.2</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>22.9</v>
+        <v>14.9</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>24.2</v>
+        <v>15.6</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>28.8</v>
+        <v>15.2</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>27.7</v>
+        <v>14.8</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>26.8</v>
+        <v>14.5</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>26.1</v>
+        <v>14.3</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>30.3</v>
+        <v>14</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>29.4</v>
+        <v>13.8</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>28.7</v>
+        <v>13.6</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>32.5</v>
+        <v>13.4</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>36.7</v>
+        <v>13.3</v>
       </c>
       <c r="R9" s="9" t="n">
-        <v>31.4</v>
+        <v>17.3</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="T9" s="9" t="n">
-        <v>38.9</v>
+        <v>12.6</v>
       </c>
       <c r="U9" s="9" t="n">
-        <v>38</v>
+        <v>12.5</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>37.2</v>
+        <v>16.5</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>41</v>
+        <v>12.3</v>
       </c>
       <c r="X9" s="9" t="n">
-        <v>36.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y9" s="9" t="n">
-        <v>35.7</v>
+        <v>16.2</v>
       </c>
       <c r="Z9" s="10" t="n">
-        <v>29</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="11">
@@ -5924,7 +6106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -6059,264 +6241,298 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20,000,000 UZS/oy</t>
+          <t>40,000,000 UZS/oy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5 restoran + 15 oila — FAKT</t>
+          <t>12 restoran + 15 oila obuna + ~205 chakana xarid — FAKT</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Asoschi allaqachon kiritgan</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>$50,000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>shaxsiy mablag', tashqi investitsiyasiz</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>DAROMAD</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Jami daromad</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2,180,625,000 UZS</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>$167,740</t>
-        </is>
-      </c>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>DAROMAD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Oxirgi oy daromadi</t>
+          <t>Jami daromad</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>165,750,000 UZS</t>
+          <t>2,317,625,000 UZS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>$12,750</t>
+          <t>$178,279</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MRR (oxirgi oy)</t>
+          <t>Oxirgi oy daromadi</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>141,000,000 UZS</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>142,750,000 UZS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>$10,981</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>MRR (oxirgi oy)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>65,000,000 UZS</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>ARR (oxirgi oy)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1,692,000,000 UZS</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>$130,154</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>780,000,000 UZS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>$60,000</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>FOYDA</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Jami sof foyda</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>874,696,107 UZS</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>$67,284</t>
-        </is>
-      </c>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>FOYDA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EBITDA marja (o'rtacha)</t>
+          <t>Jami sof foyda</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>764,716,107 UZS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>soliqqacha</t>
+          <t>$58,824</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Break-even</t>
+          <t>EBITDA marja (o'rtacha)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sep'26</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kompaniya bugun ham foydali — investitsiya o'sish uchun</t>
+          <t>soliqqacha</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Break-even</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sep'26</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>kompaniya bugun ham foydali — investitsiya o'sish uchun</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>ROI (24 oy)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>192%</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>168%</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>transh kelgan kundan hisoblanadi</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-    </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>MIJOZLAR</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Oxirgi oy</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>30 restoran + 132 oila</t>
-        </is>
-      </c>
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>MIJOZLAR</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Churn (oylik)</t>
+          <t>Doimiy mijozlar (M24)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>35 restoran + 60 oila obuna</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Chakana xaridlar (M24)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>530/oy</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>o'rtacha chek 100,000 so'm</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Churn (oylik)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>LTV/CAC (o'rtacha)</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>29.0x</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>13.6x</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>formula 7-varaqda</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>KASSA</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Kassa qoldig'i (M24)</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1,876,431,000 UZS</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>$144,341</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1,807,551,000 UZS</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>$139,042</t>
         </is>
       </c>
     </row>

--- a/doc/ready/Fin_Model_Microgreen_Uzbekistan.xlsx
+++ b/doc/ready/Fin_Model_Microgreen_Uzbekistan.xlsx
@@ -521,7 +521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M1 — bugungi FAKT: 12 restoran + 15 oila (obuna) + ~205 chakana xarid = 40,000,000 so'm/oy. O'sish shu nuqtadan.</t>
+          <t>M1 — bugungi FAKT: 12 restoran + 15 oila (obuna) + ~205 chakana xarid = 35,714,286 so'm/oy. O'sish shu nuqtadan.</t>
         </is>
       </c>
     </row>
@@ -1302,928 +1302,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Z13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>3. DAROMAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Ko'rsatkich (UZS)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Sep'26</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Oct'26</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Nov'26</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Dec'26</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Jan'27</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Feb'27</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Mar'27</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Apr'27</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>May'27</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Jun'27</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Jul'27</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>Aug'27</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>Sep'27</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>Oct'27</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>Nov'27</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>Dec'27</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>Jan'28</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>Feb'28</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>Mar'28</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>Apr'28</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>May'28</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>Jun'28</t>
-        </is>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>Jul'28</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>Aug'28</t>
-        </is>
-      </c>
-      <c r="Z3" s="4" t="inlineStr">
-        <is>
-          <t>JAMI</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Restoranlar (buyurtma)</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>13000000</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>14000000</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>17000000</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>19000000</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>23000000</v>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v>24000000</v>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v>26000000</v>
-      </c>
-      <c r="R4" s="5" t="n">
-        <v>27000000</v>
-      </c>
-      <c r="S4" s="5" t="n">
-        <v>28000000</v>
-      </c>
-      <c r="T4" s="5" t="n">
-        <v>29000000</v>
-      </c>
-      <c r="U4" s="5" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="V4" s="5" t="n">
-        <v>31000000</v>
-      </c>
-      <c r="W4" s="5" t="n">
-        <v>32000000</v>
-      </c>
-      <c r="X4" s="5" t="n">
-        <v>33000000</v>
-      </c>
-      <c r="Y4" s="5" t="n">
-        <v>35000000</v>
-      </c>
-      <c r="Z4" s="6" t="n">
-        <v>542000000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Oila obunalari</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>11000000</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>13000000</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>14000000</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>17000000</v>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v>19000000</v>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="Q5" s="5" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="R5" s="5" t="n">
-        <v>22500000</v>
-      </c>
-      <c r="S5" s="5" t="n">
-        <v>24000000</v>
-      </c>
-      <c r="T5" s="5" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="U5" s="5" t="n">
-        <v>26000000</v>
-      </c>
-      <c r="V5" s="5" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="W5" s="5" t="n">
-        <v>28500000</v>
-      </c>
-      <c r="X5" s="5" t="n">
-        <v>29000000</v>
-      </c>
-      <c r="Y5" s="5" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="Z5" s="6" t="n">
-        <v>431500000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Chakana savdo</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>20500000</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>23000000</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>24500000</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>26000000</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>29000000</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>30500000</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>32000000</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>33500000</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>35000000</v>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>36500000</v>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v>38000000</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>39500000</v>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v>41000000</v>
-      </c>
-      <c r="R6" s="5" t="n">
-        <v>42500000</v>
-      </c>
-      <c r="S6" s="5" t="n">
-        <v>44000000</v>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>45500000</v>
-      </c>
-      <c r="U6" s="5" t="n">
-        <v>47000000</v>
-      </c>
-      <c r="V6" s="5" t="n">
-        <v>48500000</v>
-      </c>
-      <c r="W6" s="5" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="X6" s="5" t="n">
-        <v>51500000</v>
-      </c>
-      <c r="Y6" s="5" t="n">
-        <v>53000000</v>
-      </c>
-      <c r="Z6" s="6" t="n">
-        <v>861500000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Qulupnay</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>6187500</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>12375000</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>18562500</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>24750000</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>24750000</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>24750000</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>24750000</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>24750000</v>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>24750000</v>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>24750000</v>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v>24750000</v>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v>24750000</v>
-      </c>
-      <c r="Q7" s="5" t="n">
-        <v>24750000</v>
-      </c>
-      <c r="R7" s="5" t="n">
-        <v>24750000</v>
-      </c>
-      <c r="S7" s="5" t="n">
-        <v>24750000</v>
-      </c>
-      <c r="T7" s="5" t="n">
-        <v>24750000</v>
-      </c>
-      <c r="U7" s="5" t="n">
-        <v>24750000</v>
-      </c>
-      <c r="V7" s="5" t="n">
-        <v>24750000</v>
-      </c>
-      <c r="W7" s="5" t="n">
-        <v>24750000</v>
-      </c>
-      <c r="X7" s="5" t="n">
-        <v>24750000</v>
-      </c>
-      <c r="Y7" s="5" t="n">
-        <v>24750000</v>
-      </c>
-      <c r="Z7" s="6" t="n">
-        <v>482625000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>JAMI DAROMAD</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>41000000</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>43500000</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>52187500</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>61875000</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>71562500</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>81250000</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>84750000</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>88250000</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>91750000</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>95250000</v>
-      </c>
-      <c r="M8" s="8" t="n">
-        <v>98750000</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>102250000</v>
-      </c>
-      <c r="O8" s="8" t="n">
-        <v>105750000</v>
-      </c>
-      <c r="P8" s="8" t="n">
-        <v>109250000</v>
-      </c>
-      <c r="Q8" s="8" t="n">
-        <v>112750000</v>
-      </c>
-      <c r="R8" s="8" t="n">
-        <v>116750000</v>
-      </c>
-      <c r="S8" s="8" t="n">
-        <v>120750000</v>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v>124250000</v>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v>127750000</v>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v>131750000</v>
-      </c>
-      <c r="W8" s="8" t="n">
-        <v>135250000</v>
-      </c>
-      <c r="X8" s="8" t="n">
-        <v>138250000</v>
-      </c>
-      <c r="Y8" s="8" t="n">
-        <v>142750000</v>
-      </c>
-      <c r="Z8" s="6" t="n">
-        <v>2317625000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MRR (takrorlanuvchi)</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>19500000</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>21500000</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>23000000</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>27000000</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>29000000</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>31000000</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>33000000</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>35000000</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>37000000</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>39000000</v>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>41000000</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>43000000</v>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>47000000</v>
-      </c>
-      <c r="R10" s="5" t="n">
-        <v>49500000</v>
-      </c>
-      <c r="S10" s="5" t="n">
-        <v>52000000</v>
-      </c>
-      <c r="T10" s="5" t="n">
-        <v>54000000</v>
-      </c>
-      <c r="U10" s="5" t="n">
-        <v>56000000</v>
-      </c>
-      <c r="V10" s="5" t="n">
-        <v>58500000</v>
-      </c>
-      <c r="W10" s="5" t="n">
-        <v>60500000</v>
-      </c>
-      <c r="X10" s="5" t="n">
-        <v>62000000</v>
-      </c>
-      <c r="Y10" s="5" t="n">
-        <v>65000000</v>
-      </c>
-      <c r="Z10" s="6" t="n">
-        <v>65000000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ARR (yillik)</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>234000000</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>240000000</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>258000000</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>276000000</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>300000000</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>324000000</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>348000000</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>372000000</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>396000000</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>420000000</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>444000000</v>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>468000000</v>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>492000000</v>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v>516000000</v>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v>540000000</v>
-      </c>
-      <c r="Q11" s="5" t="n">
-        <v>564000000</v>
-      </c>
-      <c r="R11" s="5" t="n">
-        <v>594000000</v>
-      </c>
-      <c r="S11" s="5" t="n">
-        <v>624000000</v>
-      </c>
-      <c r="T11" s="5" t="n">
-        <v>648000000</v>
-      </c>
-      <c r="U11" s="5" t="n">
-        <v>672000000</v>
-      </c>
-      <c r="V11" s="5" t="n">
-        <v>702000000</v>
-      </c>
-      <c r="W11" s="5" t="n">
-        <v>726000000</v>
-      </c>
-      <c r="X11" s="5" t="n">
-        <v>744000000</v>
-      </c>
-      <c r="Y11" s="5" t="n">
-        <v>780000000</v>
-      </c>
-      <c r="Z11" s="6" t="n">
-        <v>780000000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ARPU</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>1481481</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>1464286</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>1450000</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>1630859</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>1767857</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>1883224</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>1981707</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>1926136</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>1877660</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>1835000</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>1797170</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>1763393</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>1733051</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>1705645</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>1680769</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>1658088</v>
-      </c>
-      <c r="R12" s="5" t="n">
-        <v>1621528</v>
-      </c>
-      <c r="S12" s="5" t="n">
-        <v>1588816</v>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>1572785</v>
-      </c>
-      <c r="U12" s="5" t="n">
-        <v>1557927</v>
-      </c>
-      <c r="V12" s="5" t="n">
-        <v>1531977</v>
-      </c>
-      <c r="W12" s="5" t="n">
-        <v>1519663</v>
-      </c>
-      <c r="X12" s="5" t="n">
-        <v>1519231</v>
-      </c>
-      <c r="Y12" s="5" t="n">
-        <v>1502632</v>
-      </c>
-      <c r="Z12" s="6" t="n">
-        <v>1502632</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Daromad ($)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>3077</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>3154</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>3346</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>4014</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>4760</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>5505</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>6250</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>6519</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>6788</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>7058</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>7327</v>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v>7596</v>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>7865</v>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v>8135</v>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v>8404</v>
-      </c>
-      <c r="Q13" s="5" t="n">
-        <v>8673</v>
-      </c>
-      <c r="R13" s="5" t="n">
-        <v>8981</v>
-      </c>
-      <c r="S13" s="5" t="n">
-        <v>9288</v>
-      </c>
-      <c r="T13" s="5" t="n">
-        <v>9558</v>
-      </c>
-      <c r="U13" s="5" t="n">
-        <v>9827</v>
-      </c>
-      <c r="V13" s="5" t="n">
-        <v>10135</v>
-      </c>
-      <c r="W13" s="5" t="n">
-        <v>10404</v>
-      </c>
-      <c r="X13" s="5" t="n">
-        <v>10635</v>
-      </c>
-      <c r="Y13" s="5" t="n">
-        <v>10981</v>
-      </c>
-      <c r="Z13" s="6" t="n">
-        <v>178279</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:Z1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2263,14 +1341,14 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>4. XARAJATLAR</t>
+          <t>3. DAROMAD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Xarajat turi (UZS)</t>
+          <t>Ko'rsatkich (UZS)</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2402,985 +1480,903 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ish haqi</t>
+          <t>Mijozlar to'lovi (QQS bilan)</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>6000000</v>
+        <v>40000000</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>6000000</v>
+        <v>41000000</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>6000000</v>
+        <v>43500000</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>10000000</v>
+        <v>52187500</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>10000000</v>
+        <v>61875000</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>10000000</v>
+        <v>71562500</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>10000000</v>
+        <v>81250000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>10000000</v>
+        <v>84750000</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>10000000</v>
+        <v>88250000</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>10000000</v>
+        <v>91750000</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>10000000</v>
+        <v>95250000</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>10000000</v>
+        <v>98750000</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>10000000</v>
+        <v>102250000</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>10000000</v>
+        <v>105750000</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>10000000</v>
+        <v>109250000</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>10000000</v>
+        <v>112750000</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>10000000</v>
+        <v>116750000</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>10000000</v>
+        <v>120750000</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>10000000</v>
+        <v>124250000</v>
       </c>
       <c r="U4" s="5" t="n">
-        <v>10000000</v>
+        <v>127750000</v>
       </c>
       <c r="V4" s="5" t="n">
-        <v>10000000</v>
+        <v>131750000</v>
       </c>
       <c r="W4" s="5" t="n">
-        <v>10000000</v>
+        <v>135250000</v>
       </c>
       <c r="X4" s="5" t="n">
-        <v>10000000</v>
+        <v>138250000</v>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>10000000</v>
+        <v>142750000</v>
       </c>
       <c r="Z4" s="6" t="n">
-        <v>228000000</v>
+        <v>2317625000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ijara + kommunal</t>
+          <t>QQS (12%)</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>2000000</v>
+        <v>4285714</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2000000</v>
+        <v>4392857</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2000000</v>
+        <v>4660714</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2000000</v>
+        <v>5591518</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>2000000</v>
+        <v>6629465</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>2000000</v>
+        <v>7667410</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>3000000</v>
+        <v>8705358</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>3000000</v>
+        <v>9080357</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>3000000</v>
+        <v>9455357</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>3000000</v>
+        <v>9830357</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>3000000</v>
+        <v>10205358</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>3000000</v>
+        <v>10580358</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>3000000</v>
+        <v>10955357</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>3000000</v>
+        <v>11330358</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>3000000</v>
+        <v>11705357</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>3000000</v>
+        <v>12080357</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>3000000</v>
+        <v>12508928</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>3000000</v>
+        <v>12937501</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>3000000</v>
+        <v>13312500</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>3000000</v>
+        <v>13687500</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>3000000</v>
+        <v>14116073</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>3000000</v>
+        <v>14491071</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>3000000</v>
+        <v>14812500</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>3000000</v>
+        <v>15294643</v>
       </c>
       <c r="Z5" s="6" t="n">
-        <v>66000000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Elektr energiya</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="R6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="S6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="U6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="V6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="W6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="X6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="Y6" s="5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="Z6" s="6" t="n">
-        <v>135000000</v>
+        <v>248316968</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Materiallar</t>
+          <t>Restoranlar (buyurtma)</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>2000000</v>
+        <v>10714286</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>2000000</v>
+        <v>10714286</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2000000</v>
+        <v>11607143</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3500000</v>
+        <v>12500000</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>3500000</v>
+        <v>13392857</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>3500000</v>
+        <v>14285714</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>3500000</v>
+        <v>15178571</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>3500000</v>
+        <v>16071429</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>3500000</v>
+        <v>16964286</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>3500000</v>
+        <v>17857143</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>3500000</v>
+        <v>18750000</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>3500000</v>
+        <v>19642857</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>3500000</v>
+        <v>20535714</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>3500000</v>
+        <v>21428571</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>3500000</v>
+        <v>22321429</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>3500000</v>
+        <v>23214286</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>3500000</v>
+        <v>24107143</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>3500000</v>
+        <v>25000000</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>3500000</v>
+        <v>25892857</v>
       </c>
       <c r="U7" s="5" t="n">
-        <v>3500000</v>
+        <v>26785714</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>3500000</v>
+        <v>27678571</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>3500000</v>
+        <v>28571429</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>3500000</v>
+        <v>29464286</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>3500000</v>
+        <v>31250000</v>
       </c>
       <c r="Z7" s="6" t="n">
-        <v>79500000</v>
+        <v>483928572</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Oila obunalari</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1500000</v>
+        <v>6696429</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1500000</v>
+        <v>7142857</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1500000</v>
+        <v>7589286</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2000000</v>
+        <v>8035714</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>2000000</v>
+        <v>8928571</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>2000000</v>
+        <v>9821429</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>2000000</v>
+        <v>10714286</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>2000000</v>
+        <v>11607143</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>2000000</v>
+        <v>12500000</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>2000000</v>
+        <v>13392857</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>2000000</v>
+        <v>14285714</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>2000000</v>
+        <v>15178571</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>2000000</v>
+        <v>16071429</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>2000000</v>
+        <v>16964286</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>2000000</v>
+        <v>17857143</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>2000000</v>
+        <v>18750000</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>2000000</v>
+        <v>20089286</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>2000000</v>
+        <v>21428571</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>2000000</v>
+        <v>22321429</v>
       </c>
       <c r="U8" s="5" t="n">
-        <v>2000000</v>
+        <v>23214286</v>
       </c>
       <c r="V8" s="5" t="n">
-        <v>2000000</v>
+        <v>24553571</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>2000000</v>
+        <v>25446429</v>
       </c>
       <c r="X8" s="5" t="n">
-        <v>2000000</v>
+        <v>25892857</v>
       </c>
       <c r="Y8" s="5" t="n">
-        <v>2000000</v>
+        <v>26785714</v>
       </c>
       <c r="Z8" s="6" t="n">
-        <v>46500000</v>
+        <v>385267858</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Chakana savdo</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1500000</v>
+        <v>18303571</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1500000</v>
+        <v>18750000</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1500000</v>
+        <v>19642857</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2000000</v>
+        <v>20535714</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>2000000</v>
+        <v>21875000</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>2000000</v>
+        <v>23214286</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>2000000</v>
+        <v>24553571</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>2000000</v>
+        <v>25892857</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>2000000</v>
+        <v>27232143</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>2000000</v>
+        <v>28571429</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>2000000</v>
+        <v>29910714</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>2000000</v>
+        <v>31250000</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>2000000</v>
+        <v>32589286</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>2000000</v>
+        <v>33928571</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>2000000</v>
+        <v>35267857</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>2000000</v>
+        <v>36607143</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>2000000</v>
+        <v>37946429</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>2000000</v>
+        <v>39285714</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>2000000</v>
+        <v>40625000</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v>2000000</v>
+        <v>41964286</v>
       </c>
       <c r="V9" s="5" t="n">
-        <v>2000000</v>
+        <v>43303571</v>
       </c>
       <c r="W9" s="5" t="n">
-        <v>2000000</v>
+        <v>44642857</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>2000000</v>
+        <v>45982143</v>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>2000000</v>
+        <v>47321429</v>
       </c>
       <c r="Z9" s="6" t="n">
-        <v>46500000</v>
+        <v>769196428</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Boshqa</t>
+          <t>Qulupnay</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>800000</v>
+        <v>5524554</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>800000</v>
+        <v>11049107</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>800000</v>
+        <v>16573661</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>800000</v>
+        <v>22098214</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>800000</v>
+        <v>22098214</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>800000</v>
+        <v>22098214</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>800000</v>
+        <v>22098214</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>800000</v>
+        <v>22098214</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>800000</v>
+        <v>22098214</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>800000</v>
+        <v>22098214</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>800000</v>
+        <v>22098214</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>800000</v>
+        <v>22098214</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>800000</v>
+        <v>22098214</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>800000</v>
+        <v>22098214</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>800000</v>
+        <v>22098214</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>800000</v>
+        <v>22098214</v>
       </c>
       <c r="U10" s="5" t="n">
-        <v>800000</v>
+        <v>22098214</v>
       </c>
       <c r="V10" s="5" t="n">
-        <v>800000</v>
+        <v>22098214</v>
       </c>
       <c r="W10" s="5" t="n">
-        <v>800000</v>
+        <v>22098214</v>
       </c>
       <c r="X10" s="5" t="n">
-        <v>800000</v>
+        <v>22098214</v>
       </c>
       <c r="Y10" s="5" t="n">
-        <v>800000</v>
+        <v>22098214</v>
       </c>
       <c r="Z10" s="6" t="n">
-        <v>18300000</v>
+        <v>430915174</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Soliq (4%)</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>1640000</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>1740000</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>2087500</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>2475000</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>2862500</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>3250000</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>3390000</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>3530000</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>3670000</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>3810000</v>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>3950000</v>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>4090000</v>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v>4230000</v>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v>4370000</v>
-      </c>
-      <c r="Q11" s="5" t="n">
-        <v>4510000</v>
-      </c>
-      <c r="R11" s="5" t="n">
-        <v>4670000</v>
-      </c>
-      <c r="S11" s="5" t="n">
-        <v>4830000</v>
-      </c>
-      <c r="T11" s="5" t="n">
-        <v>4970000</v>
-      </c>
-      <c r="U11" s="5" t="n">
-        <v>5110000</v>
-      </c>
-      <c r="V11" s="5" t="n">
-        <v>5270000</v>
-      </c>
-      <c r="W11" s="5" t="n">
-        <v>5410000</v>
-      </c>
-      <c r="X11" s="5" t="n">
-        <v>5530000</v>
-      </c>
-      <c r="Y11" s="5" t="n">
-        <v>5710000</v>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>JAMI DAROMAD (QQSsiz)</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>35714286</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>36607143</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>38839286</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>46595982</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>55245535</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>63895090</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>72544642</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>75669643</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>78794643</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>81919643</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>85044642</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>88169642</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>91294643</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>94419642</v>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>97544643</v>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>100669643</v>
+      </c>
+      <c r="R11" s="8" t="n">
+        <v>104241072</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>107812499</v>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v>110937500</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>114062500</v>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v>117633927</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>120758929</v>
+      </c>
+      <c r="X11" s="8" t="n">
+        <v>123437500</v>
+      </c>
+      <c r="Y11" s="8" t="n">
+        <v>127455357</v>
       </c>
       <c r="Z11" s="6" t="n">
-        <v>92705000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>JAMI OPEX</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>18100000</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>18140000</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>18240000</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>28387500</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>28775000</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>29162500</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>30550000</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>30690000</v>
-      </c>
-      <c r="J12" s="8" t="n">
-        <v>30830000</v>
-      </c>
-      <c r="K12" s="8" t="n">
-        <v>30970000</v>
-      </c>
-      <c r="L12" s="8" t="n">
-        <v>31110000</v>
-      </c>
-      <c r="M12" s="8" t="n">
+        <v>2069308032</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MRR (takrorlanuvchi)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>17410715</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>17857143</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>19196429</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>20535714</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>22321428</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>24107143</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>25892857</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>27678572</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>29464286</v>
+      </c>
+      <c r="K13" s="5" t="n">
         <v>31250000</v>
       </c>
-      <c r="N12" s="8" t="n">
-        <v>31390000</v>
-      </c>
-      <c r="O12" s="8" t="n">
-        <v>31530000</v>
-      </c>
-      <c r="P12" s="8" t="n">
-        <v>31670000</v>
-      </c>
-      <c r="Q12" s="8" t="n">
-        <v>31810000</v>
-      </c>
-      <c r="R12" s="8" t="n">
-        <v>31970000</v>
-      </c>
-      <c r="S12" s="8" t="n">
-        <v>32130000</v>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v>32270000</v>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v>32410000</v>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v>32570000</v>
-      </c>
-      <c r="W12" s="8" t="n">
-        <v>32710000</v>
-      </c>
-      <c r="X12" s="8" t="n">
-        <v>32830000</v>
-      </c>
-      <c r="Y12" s="8" t="n">
-        <v>33010000</v>
-      </c>
-      <c r="Z12" s="6" t="n">
-        <v>712505000</v>
+      <c r="L13" s="5" t="n">
+        <v>33035714</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>34821428</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>36607143</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>38392857</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>40178572</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>41964286</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>44196429</v>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>46428571</v>
+      </c>
+      <c r="T13" s="5" t="n">
+        <v>48214286</v>
+      </c>
+      <c r="U13" s="5" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="V13" s="5" t="n">
+        <v>52232142</v>
+      </c>
+      <c r="W13" s="5" t="n">
+        <v>54017858</v>
+      </c>
+      <c r="X13" s="5" t="n">
+        <v>55357143</v>
+      </c>
+      <c r="Y13" s="5" t="n">
+        <v>58035714</v>
+      </c>
+      <c r="Z13" s="6" t="n">
+        <v>58035714</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COGS (tannarx)</t>
+          <t>ARR (yillik)</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>12000000</v>
+        <v>208928580</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>12300000</v>
+        <v>214285716</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>13050000</v>
+        <v>230357148</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>16584375</v>
+        <v>246428568</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>20418750</v>
+        <v>267857136</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>24253125</v>
+        <v>289285716</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>28087500</v>
+        <v>310714284</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>29137500</v>
+        <v>332142864</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>30187500</v>
+        <v>353571432</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>31237500</v>
+        <v>375000000</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>32287500</v>
+        <v>396428568</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>33337500</v>
+        <v>417857136</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>34387500</v>
+        <v>439285716</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>35437500</v>
+        <v>460714284</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>36487500</v>
+        <v>482142864</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>37537500</v>
+        <v>503571432</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>38737500</v>
+        <v>530357148</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>39937500</v>
+        <v>557142852</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>40987500</v>
+        <v>578571432</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>42037500</v>
+        <v>600000000</v>
       </c>
       <c r="V14" s="5" t="n">
-        <v>43237500</v>
+        <v>626785704</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>44287500</v>
+        <v>648214296</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>45187500</v>
+        <v>664285716</v>
       </c>
       <c r="Y14" s="5" t="n">
-        <v>46537500</v>
+        <v>696428568</v>
       </c>
       <c r="Z14" s="6" t="n">
-        <v>767681250</v>
+        <v>696428568</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Brutto foyda</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>28000000</v>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>28700000</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>30450000</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>35603125</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>41456250</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>47309375</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>53162500</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>55612500</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>58062500</v>
-      </c>
-      <c r="K15" s="8" t="n">
-        <v>60512500</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>62962500</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>65412500</v>
-      </c>
-      <c r="N15" s="8" t="n">
-        <v>67862500</v>
-      </c>
-      <c r="O15" s="8" t="n">
-        <v>70312500</v>
-      </c>
-      <c r="P15" s="8" t="n">
-        <v>72762500</v>
-      </c>
-      <c r="Q15" s="8" t="n">
-        <v>75212500</v>
-      </c>
-      <c r="R15" s="8" t="n">
-        <v>78012500</v>
-      </c>
-      <c r="S15" s="8" t="n">
-        <v>80812500</v>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v>83262500</v>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v>85712500</v>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v>88512500</v>
-      </c>
-      <c r="W15" s="8" t="n">
-        <v>90962500</v>
-      </c>
-      <c r="X15" s="8" t="n">
-        <v>93062500</v>
-      </c>
-      <c r="Y15" s="8" t="n">
-        <v>96212500</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ARPU</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1322751</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1307398</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1294643</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1456124</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1578444</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1681450</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1769382</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>1719765</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>1676482</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>1638393</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>1604616</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>1574458</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>1547367</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>1522897</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>1500687</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>1480436</v>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>1447793</v>
+      </c>
+      <c r="S15" s="5" t="n">
+        <v>1418586</v>
+      </c>
+      <c r="T15" s="5" t="n">
+        <v>1404272</v>
+      </c>
+      <c r="U15" s="5" t="n">
+        <v>1391006</v>
+      </c>
+      <c r="V15" s="5" t="n">
+        <v>1367836</v>
+      </c>
+      <c r="W15" s="5" t="n">
+        <v>1356842</v>
+      </c>
+      <c r="X15" s="5" t="n">
+        <v>1356456</v>
+      </c>
+      <c r="Y15" s="5" t="n">
+        <v>1341635</v>
       </c>
       <c r="Z15" s="6" t="n">
-        <v>1549943750</v>
+        <v>1341635</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brutto marja (%)</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="n">
-        <v>70</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>70</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>70</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>67</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>66</v>
-      </c>
-      <c r="L16" s="9" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="M16" s="9" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="N16" s="9" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="O16" s="9" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="P16" s="9" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="Q16" s="9" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="R16" s="9" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="S16" s="9" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="T16" s="9" t="n">
-        <v>67</v>
-      </c>
-      <c r="U16" s="9" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="V16" s="9" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="W16" s="9" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="X16" s="9" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="Y16" s="9" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="Z16" s="10" t="n">
-        <v>66.90000000000001</v>
+          <t>Daromad ($)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2747</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>2816</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2988</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>3584</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>4250</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>4915</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>5580</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>5821</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>6061</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>6302</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>6542</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>6782</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>7023</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>7263</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>7503</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>7744</v>
+      </c>
+      <c r="R16" s="5" t="n">
+        <v>8019</v>
+      </c>
+      <c r="S16" s="5" t="n">
+        <v>8293</v>
+      </c>
+      <c r="T16" s="5" t="n">
+        <v>8534</v>
+      </c>
+      <c r="U16" s="5" t="n">
+        <v>8774</v>
+      </c>
+      <c r="V16" s="5" t="n">
+        <v>9049</v>
+      </c>
+      <c r="W16" s="5" t="n">
+        <v>9289</v>
+      </c>
+      <c r="X16" s="5" t="n">
+        <v>9495</v>
+      </c>
+      <c r="Y16" s="5" t="n">
+        <v>9804</v>
+      </c>
+      <c r="Z16" s="6" t="n">
+        <v>159178</v>
       </c>
     </row>
   </sheetData>
@@ -3391,13 +2387,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3431,14 +2427,14 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5. AYLANMA MABLAG' — investitsiyaning to'liq taqsimoti</t>
+          <t>4. XARAJATLAR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ko'rsatkich (UZS)</t>
+          <t>Xarajat turi (UZS)</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3570,6 +2566,1092 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Ish haqi</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="S4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="V4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="W4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="X4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="Y4" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="Z4" s="6" t="n">
+        <v>228000000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ijara + kommunal</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="V5" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="W5" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="X5" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="Y5" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="Z5" s="6" t="n">
+        <v>66000000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Elektr energiya</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="V6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="W6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="X6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="Y6" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="Z6" s="6" t="n">
+        <v>135000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Materiallar</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="T7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="U7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="V7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="W7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="X7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="Y7" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="Z7" s="6" t="n">
+        <v>79500000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="S8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="U8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="V8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="W8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="X8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="Y8" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="Z8" s="6" t="n">
+        <v>46500000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="R9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="S9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="T9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="U9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="V9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="W9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="X9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="Y9" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="Z9" s="6" t="n">
+        <v>46500000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Boshqa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="U10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="V10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="W10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="X10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="Y10" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="Z10" s="6" t="n">
+        <v>18300000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>JAMI OPEX</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>26300000</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>26300000</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>26300000</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="R11" s="8" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="X11" s="8" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="Y11" s="8" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="Z11" s="6" t="n">
+        <v>619800000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>COGS (tannarx)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>10714286</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>10982143</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>11651786</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>14807478</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>18231027</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>21654576</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>25078125</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>26015625</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>26953125</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>27890625</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>28828125</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>29765625</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>30703125</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>31640625</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>32578125</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>33515625</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>34587054</v>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>35658482</v>
+      </c>
+      <c r="T13" s="5" t="n">
+        <v>36595982</v>
+      </c>
+      <c r="U13" s="5" t="n">
+        <v>37533482</v>
+      </c>
+      <c r="V13" s="5" t="n">
+        <v>38604910</v>
+      </c>
+      <c r="W13" s="5" t="n">
+        <v>39542411</v>
+      </c>
+      <c r="X13" s="5" t="n">
+        <v>40345982</v>
+      </c>
+      <c r="Y13" s="5" t="n">
+        <v>41551339</v>
+      </c>
+      <c r="Z13" s="6" t="n">
+        <v>685429688</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Brutto foyda</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>25625000</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>27187500</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>31788504</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>37014508</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>42240514</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>47466517</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>49654018</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>51841518</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>54029018</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>56216517</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>58404017</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>60591518</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>62779017</v>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>64966518</v>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>67154018</v>
+      </c>
+      <c r="R14" s="8" t="n">
+        <v>69654018</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>72154017</v>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v>74341518</v>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v>76529018</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>79029017</v>
+      </c>
+      <c r="W14" s="8" t="n">
+        <v>81216518</v>
+      </c>
+      <c r="X14" s="8" t="n">
+        <v>83091518</v>
+      </c>
+      <c r="Y14" s="8" t="n">
+        <v>85904018</v>
+      </c>
+      <c r="Z14" s="6" t="n">
+        <v>1383878344</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Brutto marja (%)</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="M15" s="9" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="N15" s="9" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="O15" s="9" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="P15" s="9" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="Q15" s="9" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="R15" s="9" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="S15" s="9" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="T15" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="U15" s="9" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="V15" s="9" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="W15" s="9" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="X15" s="9" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="Y15" s="9" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="Z15" s="10" t="n">
+        <v>66.90000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:Z1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>5. AYLANMA MABLAG' — investitsiyaning to'liq taqsimoti</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Ko'rsatkich (UZS)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Sep'26</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Nov'26</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Dec'26</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Jan'27</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Feb'27</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Mar'27</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Apr'27</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>May'27</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Jun'27</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Jul'27</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Aug'27</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Sep'27</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>Oct'27</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Nov'27</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>Dec'27</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>Jan'28</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>Feb'28</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Mar'28</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>Apr'28</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>May'28</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>Jun'28</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Jul'28</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>Aug'28</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>JAMI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Investitsiya kirimi</t>
         </is>
       </c>
@@ -3652,7 +3734,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Daromad kirimi</t>
+          <t>Mijozlardan tushum (QQS bilan)</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
@@ -3980,329 +4062,575 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>COGS (xarid, tannarx)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>10714286</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>10982143</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>11651786</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>14807478</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>18231027</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>21654576</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>25078125</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>26015625</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>26953125</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>27890625</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>28828125</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>29765625</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>30703125</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>31640625</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>32578125</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>33515625</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>34587054</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>35658482</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>36595982</v>
+      </c>
+      <c r="U10" s="5" t="n">
+        <v>37533482</v>
+      </c>
+      <c r="V10" s="5" t="n">
+        <v>38604910</v>
+      </c>
+      <c r="W10" s="5" t="n">
+        <v>39542411</v>
+      </c>
+      <c r="X10" s="5" t="n">
+        <v>40345982</v>
+      </c>
+      <c r="Y10" s="5" t="n">
+        <v>41551339</v>
+      </c>
+      <c r="Z10" s="6" t="n">
+        <v>685429688</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>OPEX</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>18100000</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>18140000</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>18240000</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>28387500</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>28775000</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>29162500</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>30550000</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>30690000</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>30830000</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>30970000</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>31110000</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>31250000</v>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>31390000</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>31530000</v>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>31670000</v>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>31810000</v>
-      </c>
-      <c r="R10" s="5" t="n">
-        <v>31970000</v>
-      </c>
-      <c r="S10" s="5" t="n">
-        <v>32130000</v>
-      </c>
-      <c r="T10" s="5" t="n">
-        <v>32270000</v>
-      </c>
-      <c r="U10" s="5" t="n">
-        <v>32410000</v>
-      </c>
-      <c r="V10" s="5" t="n">
-        <v>32570000</v>
-      </c>
-      <c r="W10" s="5" t="n">
-        <v>32710000</v>
-      </c>
-      <c r="X10" s="5" t="n">
-        <v>32830000</v>
-      </c>
-      <c r="Y10" s="5" t="n">
-        <v>33010000</v>
-      </c>
-      <c r="Z10" s="6" t="n">
-        <v>712505000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>JAMI CHIQIM</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>275669000</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>18140000</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>18240000</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>28387500</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>28775000</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>29162500</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>30550000</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>30690000</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>30830000</v>
-      </c>
-      <c r="K11" s="8" t="n">
-        <v>30970000</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>31110000</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>31250000</v>
-      </c>
-      <c r="N11" s="8" t="n">
-        <v>31390000</v>
-      </c>
-      <c r="O11" s="8" t="n">
-        <v>31530000</v>
-      </c>
-      <c r="P11" s="8" t="n">
-        <v>31670000</v>
-      </c>
-      <c r="Q11" s="8" t="n">
-        <v>31810000</v>
-      </c>
-      <c r="R11" s="8" t="n">
-        <v>31970000</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>32130000</v>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v>32270000</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>32410000</v>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v>32570000</v>
-      </c>
-      <c r="W11" s="8" t="n">
-        <v>32710000</v>
-      </c>
-      <c r="X11" s="8" t="n">
-        <v>32830000</v>
-      </c>
-      <c r="Y11" s="8" t="n">
-        <v>33010000</v>
+      <c r="B11" s="5" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>26300000</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>26300000</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>26300000</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="S11" s="5" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="T11" s="5" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="U11" s="5" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="V11" s="5" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="W11" s="5" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="X11" s="5" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="Y11" s="5" t="n">
+        <v>27300000</v>
       </c>
       <c r="Z11" s="6" t="n">
-        <v>970074000</v>
+        <v>619800000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QQS to'lovi</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>4285714</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4392857</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4660714</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5591518</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>6629465</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>7667410</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>8705358</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>9080357</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>9455357</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>9830357</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>10205358</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>10580358</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>10955357</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>11330358</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>11705357</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>12080357</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>12508928</v>
+      </c>
+      <c r="S12" s="5" t="n">
+        <v>12937501</v>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>13312500</v>
+      </c>
+      <c r="U12" s="5" t="n">
+        <v>13687500</v>
+      </c>
+      <c r="V12" s="5" t="n">
+        <v>14116073</v>
+      </c>
+      <c r="W12" s="5" t="n">
+        <v>14491071</v>
+      </c>
+      <c r="X12" s="5" t="n">
+        <v>14812500</v>
+      </c>
+      <c r="Y12" s="5" t="n">
+        <v>15294643</v>
+      </c>
+      <c r="Z12" s="6" t="n">
+        <v>248316968</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>SOF PUL OQIMI</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>219331000</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>22860000</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>25260000</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>23800000</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>33100000</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>42400000</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>50700000</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>54060000</v>
-      </c>
-      <c r="J13" s="8" t="n">
-        <v>57420000</v>
-      </c>
-      <c r="K13" s="8" t="n">
-        <v>60780000</v>
-      </c>
-      <c r="L13" s="8" t="n">
-        <v>64140000</v>
-      </c>
-      <c r="M13" s="8" t="n">
-        <v>67500000</v>
-      </c>
-      <c r="N13" s="8" t="n">
-        <v>70860000</v>
-      </c>
-      <c r="O13" s="8" t="n">
-        <v>74220000</v>
-      </c>
-      <c r="P13" s="8" t="n">
-        <v>77580000</v>
-      </c>
-      <c r="Q13" s="8" t="n">
-        <v>80940000</v>
-      </c>
-      <c r="R13" s="8" t="n">
-        <v>84780000</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>88620000</v>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v>91980000</v>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v>95340000</v>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v>99180000</v>
-      </c>
-      <c r="W13" s="8" t="n">
-        <v>102540000</v>
-      </c>
-      <c r="X13" s="8" t="n">
-        <v>105420000</v>
-      </c>
-      <c r="Y13" s="8" t="n">
-        <v>109740000</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Foyda solig'i</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>1020000</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1095000</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1282500</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>243063</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>870183</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>1497304</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>2004424</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>2266924</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>2529424</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>2791924</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>3054424</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>3316924</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>3579424</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>3841924</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>4104424</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>4366924</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>4666924</v>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>4966924</v>
+      </c>
+      <c r="T13" s="5" t="n">
+        <v>5229424</v>
+      </c>
+      <c r="U13" s="5" t="n">
+        <v>5491924</v>
+      </c>
+      <c r="V13" s="5" t="n">
+        <v>5791924</v>
+      </c>
+      <c r="W13" s="5" t="n">
+        <v>6054424</v>
+      </c>
+      <c r="X13" s="5" t="n">
+        <v>6279424</v>
+      </c>
+      <c r="Y13" s="5" t="n">
+        <v>6616924</v>
       </c>
       <c r="Z13" s="6" t="n">
-        <v>1802551000</v>
+        <v>82962682</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
+          <t>JAMI CHIQIM</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>290089000</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>32970000</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>34095000</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>46942059</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>52030675</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>57119290</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>63087907</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>64662906</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>66237906</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>67812906</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>69387907</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>70962907</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>72537906</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>74112907</v>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>75687906</v>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>77262906</v>
+      </c>
+      <c r="R14" s="8" t="n">
+        <v>79062906</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>80862907</v>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v>82437906</v>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v>84012906</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>85812907</v>
+      </c>
+      <c r="W14" s="8" t="n">
+        <v>87387906</v>
+      </c>
+      <c r="X14" s="8" t="n">
+        <v>88737906</v>
+      </c>
+      <c r="Y14" s="8" t="n">
+        <v>90762906</v>
+      </c>
+      <c r="Z14" s="6" t="n">
+        <v>1894078338</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>SOF PUL OQIMI</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>204911000</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>8030000</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>9405000</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>5245441</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>9844325</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>14443210</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>18162093</v>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>20087094</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>22012094</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>23937094</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>25862093</v>
+      </c>
+      <c r="M16" s="8" t="n">
+        <v>27787093</v>
+      </c>
+      <c r="N16" s="8" t="n">
+        <v>29712094</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>31637093</v>
+      </c>
+      <c r="P16" s="8" t="n">
+        <v>33562094</v>
+      </c>
+      <c r="Q16" s="8" t="n">
+        <v>35487094</v>
+      </c>
+      <c r="R16" s="8" t="n">
+        <v>37687094</v>
+      </c>
+      <c r="S16" s="8" t="n">
+        <v>39887093</v>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v>41812094</v>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v>43737094</v>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v>45937093</v>
+      </c>
+      <c r="W16" s="8" t="n">
+        <v>47862094</v>
+      </c>
+      <c r="X16" s="8" t="n">
+        <v>49512094</v>
+      </c>
+      <c r="Y16" s="8" t="n">
+        <v>51987094</v>
+      </c>
+      <c r="Z16" s="6" t="n">
+        <v>878546662</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
           <t>KASSA QOLDIG'I</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
-        <v>224331000</v>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>247191000</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>272451000</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>296251000</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>329351000</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>371751000</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>422451000</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>476511000</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>533931000</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>594711000</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>658851000</v>
-      </c>
-      <c r="M14" s="8" t="n">
-        <v>726351000</v>
-      </c>
-      <c r="N14" s="8" t="n">
-        <v>797211000</v>
-      </c>
-      <c r="O14" s="8" t="n">
-        <v>871431000</v>
-      </c>
-      <c r="P14" s="8" t="n">
-        <v>949011000</v>
-      </c>
-      <c r="Q14" s="8" t="n">
-        <v>1029951000</v>
-      </c>
-      <c r="R14" s="8" t="n">
-        <v>1114731000</v>
-      </c>
-      <c r="S14" s="8" t="n">
-        <v>1203351000</v>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v>1295331000</v>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v>1390671000</v>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v>1489851000</v>
-      </c>
-      <c r="W14" s="8" t="n">
-        <v>1592391000</v>
-      </c>
-      <c r="X14" s="8" t="n">
-        <v>1697811000</v>
-      </c>
-      <c r="Y14" s="8" t="n">
-        <v>1807551000</v>
-      </c>
-      <c r="Z14" s="6" t="n">
-        <v>1807551000</v>
+      <c r="B17" s="8" t="n">
+        <v>209911000</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>217941000</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>227346000</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>232591441</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>242435766</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>256878976</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>275041069</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>295128163</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>317140257</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>341077351</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>366939444</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>394726537</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>424438631</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>456075724</v>
+      </c>
+      <c r="P17" s="8" t="n">
+        <v>489637818</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>525124912</v>
+      </c>
+      <c r="R17" s="8" t="n">
+        <v>562812006</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>602699099</v>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v>644511193</v>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v>688248287</v>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v>734185380</v>
+      </c>
+      <c r="W17" s="8" t="n">
+        <v>782047474</v>
+      </c>
+      <c r="X17" s="8" t="n">
+        <v>831559568</v>
+      </c>
+      <c r="Y17" s="8" t="n">
+        <v>883546662</v>
+      </c>
+      <c r="Z17" s="6" t="n">
+        <v>883546662</v>
       </c>
     </row>
   </sheetData>
@@ -4492,83 +4820,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jami daromad</t>
+          <t>Jami daromad (QQSsiz)</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>40000000</v>
+        <v>35714286</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>41000000</v>
+        <v>36607143</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>43500000</v>
+        <v>38839286</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>52187500</v>
+        <v>46595982</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>61875000</v>
+        <v>55245535</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>71562500</v>
+        <v>63895090</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>81250000</v>
+        <v>72544642</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>84750000</v>
+        <v>75669643</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>88250000</v>
+        <v>78794643</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>91750000</v>
+        <v>81919643</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>95250000</v>
+        <v>85044642</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>98750000</v>
+        <v>88169642</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>102250000</v>
+        <v>91294643</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>105750000</v>
+        <v>94419642</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>109250000</v>
+        <v>97544643</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>112750000</v>
+        <v>100669643</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>116750000</v>
+        <v>104241072</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>120750000</v>
+        <v>107812499</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>124250000</v>
+        <v>110937500</v>
       </c>
       <c r="U4" s="5" t="n">
-        <v>127750000</v>
+        <v>114062500</v>
       </c>
       <c r="V4" s="5" t="n">
-        <v>131750000</v>
+        <v>117633927</v>
       </c>
       <c r="W4" s="5" t="n">
-        <v>135250000</v>
+        <v>120758929</v>
       </c>
       <c r="X4" s="5" t="n">
-        <v>138250000</v>
+        <v>123437500</v>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>142750000</v>
+        <v>127455357</v>
       </c>
       <c r="Z4" s="6" t="n">
-        <v>2317625000</v>
+        <v>2069308032</v>
       </c>
     </row>
     <row r="5">
@@ -4578,79 +4906,79 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>12000000</v>
+        <v>10714286</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>12300000</v>
+        <v>10982143</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>13050000</v>
+        <v>11651786</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>16584375</v>
+        <v>14807478</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>20418750</v>
+        <v>18231027</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>24253125</v>
+        <v>21654576</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>28087500</v>
+        <v>25078125</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>29137500</v>
+        <v>26015625</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>30187500</v>
+        <v>26953125</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>31237500</v>
+        <v>27890625</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>32287500</v>
+        <v>28828125</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>33337500</v>
+        <v>29765625</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>34387500</v>
+        <v>30703125</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>35437500</v>
+        <v>31640625</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>36487500</v>
+        <v>32578125</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>37537500</v>
+        <v>33515625</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>38737500</v>
+        <v>34587054</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>39937500</v>
+        <v>35658482</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>40987500</v>
+        <v>36595982</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>42037500</v>
+        <v>37533482</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>43237500</v>
+        <v>38604910</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>44287500</v>
+        <v>39542411</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>45187500</v>
+        <v>40345982</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>46537500</v>
+        <v>41551339</v>
       </c>
       <c r="Z5" s="6" t="n">
-        <v>767681250</v>
+        <v>685429688</v>
       </c>
     </row>
     <row r="6">
@@ -4660,85 +4988,85 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>28000000</v>
+        <v>25000000</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>28700000</v>
+        <v>25625000</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>30450000</v>
+        <v>27187500</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>35603125</v>
+        <v>31788504</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>41456250</v>
+        <v>37014508</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>47309375</v>
+        <v>42240514</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>53162500</v>
+        <v>47466517</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>55612500</v>
+        <v>49654018</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>58062500</v>
+        <v>51841518</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>60512500</v>
+        <v>54029018</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>62962500</v>
+        <v>56216517</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>65412500</v>
+        <v>58404017</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>67862500</v>
+        <v>60591518</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>70312500</v>
+        <v>62779017</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>72762500</v>
+        <v>64966518</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>75212500</v>
+        <v>67154018</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>78012500</v>
+        <v>69654018</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>80812500</v>
+        <v>72154017</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>83262500</v>
+        <v>74341518</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>85712500</v>
+        <v>76529018</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>88512500</v>
+        <v>79029017</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>90962500</v>
+        <v>81216518</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>93062500</v>
+        <v>83091518</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>96212500</v>
+        <v>85904018</v>
       </c>
       <c r="Z6" s="6" t="n">
-        <v>1549943750</v>
+        <v>1383878344</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OPEX (soliqsiz)</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
@@ -4820,329 +5148,329 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>EBITDA (soliqqacha)</t>
+          <t>EBITDA</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>11500000</v>
+        <v>8500000</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>12200000</v>
+        <v>9125000</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>13950000</v>
+        <v>10687500</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>9303125</v>
+        <v>5488504</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>15156250</v>
+        <v>10714508</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>21009375</v>
+        <v>15940514</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>25862500</v>
+        <v>20166517</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>28312500</v>
+        <v>22354018</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>30762500</v>
+        <v>24541518</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>33212500</v>
+        <v>26729018</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>35662500</v>
+        <v>28916517</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>38112500</v>
+        <v>31104017</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>40562500</v>
+        <v>33291518</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>43012500</v>
+        <v>35479017</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>45462500</v>
+        <v>37666518</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>47912500</v>
+        <v>39854018</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>50712500</v>
+        <v>42354018</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>53512500</v>
+        <v>44854017</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>55962500</v>
+        <v>47041518</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>58412500</v>
+        <v>49229018</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>61212500</v>
+        <v>51729017</v>
       </c>
       <c r="W8" s="8" t="n">
-        <v>63662500</v>
+        <v>53916518</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>65762500</v>
+        <v>55791518</v>
       </c>
       <c r="Y8" s="8" t="n">
-        <v>68912500</v>
+        <v>58604018</v>
       </c>
       <c r="Z8" s="6" t="n">
-        <v>930143750</v>
+        <v>764078344</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Soliq (4%)</t>
+          <t>Amortizatsiya</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1600000</v>
+        <v>0</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1640000</v>
+        <v>0</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1740000</v>
+        <v>0</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2087500</v>
+        <v>3462983</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>2475000</v>
+        <v>3462983</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>2862500</v>
+        <v>3462983</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>3250000</v>
+        <v>3462983</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>3390000</v>
+        <v>3462983</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>3530000</v>
+        <v>3462983</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>3670000</v>
+        <v>3462983</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>3810000</v>
+        <v>3462983</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>3950000</v>
+        <v>3462983</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>4090000</v>
+        <v>3462983</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>4230000</v>
+        <v>3462983</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>4370000</v>
+        <v>3462983</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>4510000</v>
+        <v>3462983</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>4670000</v>
+        <v>3462983</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>4830000</v>
+        <v>3462983</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>4970000</v>
+        <v>3462983</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v>5110000</v>
+        <v>3462983</v>
       </c>
       <c r="V9" s="5" t="n">
-        <v>5270000</v>
+        <v>3462983</v>
       </c>
       <c r="W9" s="5" t="n">
-        <v>5410000</v>
+        <v>3462983</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>5530000</v>
+        <v>3462983</v>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>5710000</v>
+        <v>3462983</v>
       </c>
       <c r="Z9" s="6" t="n">
-        <v>92705000</v>
+        <v>72722643</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Operatsion foyda</t>
+          <t>Operatsion foyda (EBIT)</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>9900000</v>
+        <v>8500000</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>10560000</v>
+        <v>9125000</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>12210000</v>
+        <v>10687500</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>7215625</v>
+        <v>2025521</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>12681250</v>
+        <v>7251525</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>18146875</v>
+        <v>12477531</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>22612500</v>
+        <v>16703534</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>24922500</v>
+        <v>18891035</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>27232500</v>
+        <v>21078535</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>29542500</v>
+        <v>23266035</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>31852500</v>
+        <v>25453534</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>34162500</v>
+        <v>27641034</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>36472500</v>
+        <v>29828535</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>38782500</v>
+        <v>32016034</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>41092500</v>
+        <v>34203535</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>43402500</v>
+        <v>36391035</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>46042500</v>
+        <v>38891035</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>48682500</v>
+        <v>41391034</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>50992500</v>
+        <v>43578535</v>
       </c>
       <c r="U10" s="5" t="n">
-        <v>53302500</v>
+        <v>45766035</v>
       </c>
       <c r="V10" s="5" t="n">
-        <v>55942500</v>
+        <v>48266034</v>
       </c>
       <c r="W10" s="5" t="n">
-        <v>58252500</v>
+        <v>50453535</v>
       </c>
       <c r="X10" s="5" t="n">
-        <v>60232500</v>
+        <v>52328535</v>
       </c>
       <c r="Y10" s="5" t="n">
-        <v>63202500</v>
+        <v>55141035</v>
       </c>
       <c r="Z10" s="6" t="n">
-        <v>837438750</v>
+        <v>691355701</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Amortizatsiya</t>
+          <t>Foyda solig'i (12%)</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0</v>
+        <v>1020000</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0</v>
+        <v>1095000</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0</v>
+        <v>1282500</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>3462983</v>
+        <v>243063</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>3462983</v>
+        <v>870183</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>3462983</v>
+        <v>1497304</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>3462983</v>
+        <v>2004424</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>3462983</v>
+        <v>2266924</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>3462983</v>
+        <v>2529424</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>3462983</v>
+        <v>2791924</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>3462983</v>
+        <v>3054424</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>3462983</v>
+        <v>3316924</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>3462983</v>
+        <v>3579424</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>3462983</v>
+        <v>3841924</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>3462983</v>
+        <v>4104424</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>3462983</v>
+        <v>4366924</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>3462983</v>
+        <v>4666924</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>3462983</v>
+        <v>4966924</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>3462983</v>
+        <v>5229424</v>
       </c>
       <c r="U11" s="5" t="n">
-        <v>3462983</v>
+        <v>5491924</v>
       </c>
       <c r="V11" s="5" t="n">
-        <v>3462983</v>
+        <v>5791924</v>
       </c>
       <c r="W11" s="5" t="n">
-        <v>3462983</v>
+        <v>6054424</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>3462983</v>
+        <v>6279424</v>
       </c>
       <c r="Y11" s="5" t="n">
-        <v>3462983</v>
+        <v>6616924</v>
       </c>
       <c r="Z11" s="6" t="n">
-        <v>72722643</v>
+        <v>82962682</v>
       </c>
     </row>
     <row r="12">
@@ -5152,79 +5480,79 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>9900000</v>
+        <v>7480000</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>10560000</v>
+        <v>8030000</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>12210000</v>
+        <v>9405000</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3752642</v>
+        <v>1782458</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>9218267</v>
+        <v>6381342</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>14683892</v>
+        <v>10980227</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>19149517</v>
+        <v>14699110</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>21459517</v>
+        <v>16624111</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>23769517</v>
+        <v>18549111</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>26079517</v>
+        <v>20474111</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>28389517</v>
+        <v>22399110</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>30699517</v>
+        <v>24324110</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>33009517</v>
+        <v>26249111</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>35319517</v>
+        <v>28174110</v>
       </c>
       <c r="P12" s="8" t="n">
-        <v>37629517</v>
+        <v>30099111</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>39939517</v>
+        <v>32024111</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>42579517</v>
+        <v>34224111</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>45219517</v>
+        <v>36424110</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>47529517</v>
+        <v>38349111</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>49839517</v>
+        <v>40274111</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>52479517</v>
+        <v>42474110</v>
       </c>
       <c r="W12" s="8" t="n">
-        <v>54789517</v>
+        <v>44399111</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>56769517</v>
+        <v>46049111</v>
       </c>
       <c r="Y12" s="8" t="n">
-        <v>59739517</v>
+        <v>48524111</v>
       </c>
       <c r="Z12" s="6" t="n">
-        <v>764716107</v>
+        <v>608393019</v>
       </c>
     </row>
     <row r="13">
@@ -5234,79 +5562,79 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>24.8</v>
+        <v>20.9</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>25.8</v>
+        <v>21.9</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>28.1</v>
+        <v>24.2</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>14.9</v>
+        <v>11.6</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>20.5</v>
+        <v>17.2</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>23.6</v>
+        <v>20.3</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>25.3</v>
+        <v>22</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>26.9</v>
+        <v>23.5</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>28.4</v>
+        <v>25</v>
       </c>
       <c r="L13" s="9" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="N13" s="9" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="O13" s="9" t="n">
         <v>29.8</v>
       </c>
-      <c r="M13" s="9" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="N13" s="9" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="O13" s="9" t="n">
-        <v>33.4</v>
-      </c>
       <c r="P13" s="9" t="n">
-        <v>34.4</v>
+        <v>30.9</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>35.4</v>
+        <v>31.8</v>
       </c>
       <c r="R13" s="9" t="n">
-        <v>36.5</v>
+        <v>32.8</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>37.4</v>
+        <v>33.8</v>
       </c>
       <c r="T13" s="9" t="n">
-        <v>38.3</v>
+        <v>34.6</v>
       </c>
       <c r="U13" s="9" t="n">
-        <v>39</v>
+        <v>35.3</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>39.8</v>
+        <v>36.1</v>
       </c>
       <c r="W13" s="9" t="n">
-        <v>40.5</v>
+        <v>36.8</v>
       </c>
       <c r="X13" s="9" t="n">
-        <v>41.1</v>
+        <v>37.3</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>41.8</v>
+        <v>38.1</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>33</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="15">
@@ -5316,79 +5644,79 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>9900000</v>
+        <v>7480000</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>20460000</v>
+        <v>15510000</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>32670000</v>
+        <v>24915000</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>36422642</v>
+        <v>26697458</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>45640909</v>
+        <v>33078800</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>60324801</v>
+        <v>44059027</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>79474318</v>
+        <v>58758137</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>100933835</v>
+        <v>75382248</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>124703352</v>
+        <v>93931359</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>150782869</v>
+        <v>114405470</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>179172386</v>
+        <v>136804580</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>209871903</v>
+        <v>161128690</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>242881420</v>
+        <v>187377801</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>278200937</v>
+        <v>215551911</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>315830454</v>
+        <v>245651022</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>355769971</v>
+        <v>277675133</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>398349488</v>
+        <v>311899244</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>443569005</v>
+        <v>348323354</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>491098522</v>
+        <v>386672465</v>
       </c>
       <c r="U15" s="5" t="n">
-        <v>540938039</v>
+        <v>426946576</v>
       </c>
       <c r="V15" s="5" t="n">
-        <v>593417556</v>
+        <v>469420686</v>
       </c>
       <c r="W15" s="5" t="n">
-        <v>648207073</v>
+        <v>513819797</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>704976590</v>
+        <v>559868908</v>
       </c>
       <c r="Y15" s="5" t="n">
-        <v>764716107</v>
+        <v>608393019</v>
       </c>
       <c r="Z15" s="6" t="n">
-        <v>764716107</v>
+        <v>608393019</v>
       </c>
     </row>
   </sheetData>
@@ -5582,79 +5910,79 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>19500000</v>
+        <v>17410715</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>20000000</v>
+        <v>17857143</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>21500000</v>
+        <v>19196429</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>23000000</v>
+        <v>20535714</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>25000000</v>
+        <v>22321428</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>27000000</v>
+        <v>24107143</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>29000000</v>
+        <v>25892857</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>31000000</v>
+        <v>27678572</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>33000000</v>
+        <v>29464286</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>35000000</v>
+        <v>31250000</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>37000000</v>
+        <v>33035714</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>39000000</v>
+        <v>34821428</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>41000000</v>
+        <v>36607143</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>43000000</v>
+        <v>38392857</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>45000000</v>
+        <v>40178572</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>47000000</v>
+        <v>41964286</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>49500000</v>
+        <v>44196429</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>52000000</v>
+        <v>46428571</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>54000000</v>
+        <v>48214286</v>
       </c>
       <c r="U4" s="5" t="n">
-        <v>56000000</v>
+        <v>50000000</v>
       </c>
       <c r="V4" s="5" t="n">
-        <v>58500000</v>
+        <v>52232142</v>
       </c>
       <c r="W4" s="5" t="n">
-        <v>60500000</v>
+        <v>54017858</v>
       </c>
       <c r="X4" s="5" t="n">
-        <v>62000000</v>
+        <v>55357143</v>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>65000000</v>
+        <v>58035714</v>
       </c>
       <c r="Z4" s="6" t="n">
-        <v>65000000</v>
+        <v>58035714</v>
       </c>
     </row>
     <row r="5">
@@ -5664,79 +5992,79 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>234000000</v>
+        <v>208928580</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>240000000</v>
+        <v>214285716</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>258000000</v>
+        <v>230357148</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>276000000</v>
+        <v>246428568</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>300000000</v>
+        <v>267857136</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>324000000</v>
+        <v>289285716</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>348000000</v>
+        <v>310714284</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>372000000</v>
+        <v>332142864</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>396000000</v>
+        <v>353571432</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>420000000</v>
+        <v>375000000</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>444000000</v>
+        <v>396428568</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>468000000</v>
+        <v>417857136</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>492000000</v>
+        <v>439285716</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>516000000</v>
+        <v>460714284</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>540000000</v>
+        <v>482142864</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>564000000</v>
+        <v>503571432</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>594000000</v>
+        <v>530357148</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>624000000</v>
+        <v>557142852</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>648000000</v>
+        <v>578571432</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>672000000</v>
+        <v>600000000</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>702000000</v>
+        <v>626785704</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>726000000</v>
+        <v>648214296</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>744000000</v>
+        <v>664285716</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>780000000</v>
+        <v>696428568</v>
       </c>
       <c r="Z5" s="6" t="n">
-        <v>780000000</v>
+        <v>696428568</v>
       </c>
     </row>
     <row r="6">
@@ -5746,79 +6074,79 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1481481</v>
+        <v>1322751</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1464286</v>
+        <v>1307398</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1450000</v>
+        <v>1294643</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1630859</v>
+        <v>1456124</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1767857</v>
+        <v>1578444</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1883224</v>
+        <v>1681450</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1981707</v>
+        <v>1769382</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1926136</v>
+        <v>1719765</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>1877660</v>
+        <v>1676482</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>1835000</v>
+        <v>1638393</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>1797170</v>
+        <v>1604616</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>1763393</v>
+        <v>1574458</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>1733051</v>
+        <v>1547367</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>1705645</v>
+        <v>1522897</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>1680769</v>
+        <v>1500687</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>1658088</v>
+        <v>1480436</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>1621528</v>
+        <v>1447793</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>1588816</v>
+        <v>1418586</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>1572785</v>
+        <v>1404272</v>
       </c>
       <c r="U6" s="5" t="n">
-        <v>1557927</v>
+        <v>1391006</v>
       </c>
       <c r="V6" s="5" t="n">
-        <v>1531977</v>
+        <v>1367836</v>
       </c>
       <c r="W6" s="5" t="n">
-        <v>1519663</v>
+        <v>1356842</v>
       </c>
       <c r="X6" s="5" t="n">
-        <v>1519231</v>
+        <v>1356456</v>
       </c>
       <c r="Y6" s="5" t="n">
-        <v>1502632</v>
+        <v>1341635</v>
       </c>
       <c r="Z6" s="6" t="n">
-        <v>1668787</v>
+        <v>1489988</v>
       </c>
     </row>
     <row r="7">
@@ -5912,79 +6240,79 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>24888881</v>
+        <v>22222217</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>24600005</v>
+        <v>21964286</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>24360000</v>
+        <v>21750002</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>26702338</v>
+        <v>23841371</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>28427141</v>
+        <v>25381379</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>29879610</v>
+        <v>26678224</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>31119507</v>
+        <v>27785286</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>30334085</v>
+        <v>27084016</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>29648943</v>
+        <v>26472268</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>29046000</v>
+        <v>25933931</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>28511324</v>
+        <v>25456538</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>28033931</v>
+        <v>25030295</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>27605087</v>
+        <v>24647400</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>27217739</v>
+        <v>24301548</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>26866150</v>
+        <v>23987640</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>26545584</v>
+        <v>23701419</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>26004170</v>
+        <v>23218011</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>25519740</v>
+        <v>22785487</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>25294940</v>
+        <v>22584763</v>
       </c>
       <c r="U8" s="5" t="n">
-        <v>25086588</v>
+        <v>22398735</v>
       </c>
       <c r="V8" s="5" t="n">
-        <v>24701167</v>
+        <v>22054604</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>24529215</v>
+        <v>21901085</v>
       </c>
       <c r="X8" s="5" t="n">
-        <v>24543960</v>
+        <v>21914246</v>
       </c>
       <c r="Y8" s="5" t="n">
-        <v>24306323</v>
+        <v>21702062</v>
       </c>
       <c r="Z8" s="6" t="n">
-        <v>26823851</v>
+        <v>23949867</v>
       </c>
     </row>
     <row r="9">
@@ -5999,76 +6327,76 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="D9" s="9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M9" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="E9" s="9" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="I9" s="9" t="n">
+      <c r="N9" s="9" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="O9" s="9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="P9" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q9" s="9" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="R9" s="9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="S9" s="9" t="n">
         <v>15.2</v>
       </c>
-      <c r="J9" s="9" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="K9" s="9" t="n">
+      <c r="T9" s="9" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="U9" s="9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V9" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="W9" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="X9" s="9" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Y9" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="L9" s="9" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M9" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="N9" s="9" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="O9" s="9" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="P9" s="9" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Q9" s="9" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="R9" s="9" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="S9" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="T9" s="9" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="U9" s="9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="V9" s="9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="W9" s="9" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="X9" s="9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y9" s="9" t="n">
-        <v>16.2</v>
-      </c>
       <c r="Z9" s="10" t="n">
-        <v>13.6</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="11">
@@ -6106,7 +6434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -6246,293 +6574,327 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12 restoran + 15 oila obuna + ~205 chakana xarid — FAKT</t>
+          <t>12 restoran + 15 oila obuna + ~205 chakana xarid — FAKT, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t xml:space="preserve">  — QQSsiz daromad</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>35,714,286 UZS/oy</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>P&amp;L shu summadan hisoblanadi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Soliq rejimi</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>umumiy: QQS 12%</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>foyda solig'i 12% — aylanma solig'i emas</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Asoschi allaqachon kiritgan</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>$50,000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>shaxsiy mablag', tashqi investitsiyasiz</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>DAROMAD</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Jami daromad</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2,317,625,000 UZS</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>$178,279</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Oxirgi oy daromadi</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>142,750,000 UZS</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>$10,981</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MRR (oxirgi oy)</t>
+          <t>Jami daromad</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>65,000,000 UZS</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>2,069,308,032 UZS</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>$159,178</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Oxirgi oy daromadi</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>127,455,357 UZS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>$9,804</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MRR (oxirgi oy)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>58,035,714 UZS</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>ARR (oxirgi oy)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>780,000,000 UZS</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>$60,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>696,428,568 UZS</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>$53,571</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>FOYDA</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Jami sof foyda</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>764,716,107 UZS</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>$58,824</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>EBITDA marja (o'rtacha)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>40.1%</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>soliqqacha</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Break-even</t>
+          <t>Jami sof foyda</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sep'26</t>
+          <t>608,393,019 UZS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>kompaniya bugun ham foydali — investitsiya o'sish uchun</t>
+          <t>$46,799</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>EBITDA marja (o'rtacha)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>36.9%</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>soliqqacha</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Break-even</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sep'26</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>kompaniya bugun ham foydali — investitsiya o'sish uchun</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>ROI (24 oy)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>168%</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>134%</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>transh kelgan kundan hisoblanadi</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>MIJOZLAR</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Doimiy mijozlar (M24)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>35 restoran + 60 oila obuna</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Chakana xaridlar (M24)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>530/oy</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>o'rtacha chek 100,000 so'm</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Churn (oylik)</t>
+          <t>Doimiy mijozlar (M24)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>35 restoran + 60 oila obuna</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Chakana xaridlar (M24)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>530/oy</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>o'rtacha chek 100,000 so'm</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Churn (oylik)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>LTV/CAC (o'rtacha)</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>13.6x</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>12.1x</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>formula 7-varaqda</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>KASSA</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Kassa qoldig'i (M24)</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1,807,551,000 UZS</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>$139,042</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>883,546,662 UZS</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>$67,965</t>
         </is>
       </c>
     </row>
